--- a/KatalonData/IWPTestData/DisplayCFData.xlsx
+++ b/KatalonData/IWPTestData/DisplayCFData.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <mc:AlternateContent>
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\t476046\Documents\VPS-Katalon-feature-VRelay\KatalonData\IWPTestData\"/>
     </mc:Choice>
@@ -43,7 +43,7 @@
   </definedNames>
   <calcPr calcId="162913"/>
   <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+    <ext uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
   </extLst>
@@ -51,7 +51,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5216" uniqueCount="427">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5804" uniqueCount="721">
   <si>
     <t>Result</t>
   </si>
@@ -1332,12 +1332,895 @@
   </si>
   <si>
     <t>Fri Jun 12 05:09:37 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 06 22:55:20 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 06 22:57:47 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 06 22:59:20 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 06 23:00:39 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 06 23:01:47 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 06 23:02:56 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 06 23:04:13 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 06 23:05:25 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 06 23:06:39 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 06 23:08:02 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 06 23:09:15 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 06 23:10:27 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 06 23:11:35 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 06 23:12:46 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 06 23:13:54 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 06 23:15:01 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 06 23:16:08 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 06 23:17:14 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 06 23:18:28 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 06 23:19:51 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 06 23:21:05 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 06 23:22:12 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 06 23:23:18 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 06 23:24:28 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 06 23:25:36 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 06 23:26:46 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 06 23:27:58 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 06 23:29:07 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 06 23:30:08 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 06 23:31:15 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 06 23:32:31 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 06 23:33:41 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 06 23:34:47 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 06 23:35:57 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 06 23:37:04 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 06 23:38:14 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 06 23:39:30 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 06 23:40:41 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 06 23:41:46 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 06 23:43:12 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 06 23:44:29 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 06 23:45:35 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 06 23:46:48 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 06 23:48:03 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 06 23:49:19 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 06 23:50:40 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 06 23:51:53 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 06 23:53:05 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 06 23:54:19 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 06 23:55:30 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 06 23:56:49 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 06 23:57:59 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 06 23:59:15 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 07 00:00:32 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 07 00:01:52 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 07 00:03:01 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 07 00:04:04 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 07 00:05:17 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 07 00:06:38 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 07 00:07:56 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 07 00:09:03 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 07 00:10:11 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 07 00:11:19 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 07 00:12:26 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 07 00:13:34 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 07 00:14:41 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 07 00:15:52 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 07 00:16:54 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 07 00:17:59 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 07 00:19:39 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 07 00:20:57 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 07 00:22:08 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 07 00:23:11 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 07 00:24:24 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 07 00:25:36 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 07 00:26:44 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 07 00:27:51 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 07 00:28:59 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 07 00:30:16 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 07 00:31:22 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 07 00:32:30 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 07 00:33:34 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 07 00:34:39 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 07 00:35:49 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 07 00:37:03 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 07 00:38:19 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 07 00:39:34 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 07 00:40:41 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 07 00:42:04 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 07 00:43:10 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 07 00:44:17 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 07 00:45:28 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 07 00:46:37 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 07 00:47:48 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 07 00:49:33 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 07 00:50:40 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 07 00:51:42 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 07 00:52:49 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 07 00:53:57 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 07 00:55:06 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 07 00:56:12 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 07 00:57:16 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 07 00:59:08 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 07 01:00:45 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 07 01:02:23 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 07 01:04:01 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 07 01:05:44 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 07 01:07:19 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 07 01:08:27 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 07 01:09:34 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 07 01:11:10 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 07 01:12:50 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 07 01:15:04 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 07 01:16:51 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 07 01:19:17 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 07 01:21:45 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 07 01:22:55 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 07 01:24:07 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 07 01:26:23 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 07 01:28:56 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 07 01:31:38 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 07 01:33:19 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 07 01:35:16 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 07 01:36:52 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 07 01:38:25 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 07 01:39:32 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 07 01:41:09 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 07 01:42:54 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 07 01:44:36 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 07 01:46:20 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 07 01:48:04 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 07 01:50:06 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 07 01:51:21 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 07 01:52:37 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 07 01:54:23 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 07 01:56:03 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 07 01:58:18 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 07 02:00:11 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 07 02:01:56 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 07 02:03:40 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 07 02:04:54 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 07 02:06:03 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 07 02:07:42 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 07 02:09:17 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 07 02:10:57 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 07 02:12:38 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 07 02:14:16 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 07 02:16:09 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 07 02:17:51 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 07 02:19:37 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 07 02:21:00 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 07 02:22:27 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 07 02:23:48 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 07 02:25:21 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 07 02:26:59 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 07 02:28:33 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 07 02:30:02 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 07 02:31:29 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 07 02:32:48 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 07 02:34:09 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 07 02:35:23 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 07 02:36:41 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 07 02:38:09 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 07 02:39:28 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 07 02:40:54 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 07 02:42:19 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 07 02:43:41 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 07 02:45:07 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 07 02:46:26 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 07 02:47:48 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 07 02:49:06 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 07 02:50:20 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 07 02:51:35 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 07 02:52:49 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 07 02:54:20 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 07 02:55:44 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 07 02:56:59 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 07 03:00:58 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 07 03:04:43 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 07 03:08:56 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 07 03:12:35 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 07 03:16:25 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 07 03:20:40 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 07 03:24:42 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 07 03:28:27 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 07 03:32:12 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 07 03:35:49 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 07 03:39:41 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 07 03:43:40 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 07 03:47:37 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 07 03:51:40 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 07 03:55:50 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 07 03:59:42 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 07 04:03:23 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 07 04:07:14 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 07 04:11:09 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 07 04:14:51 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 07 04:18:31 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 07 04:22:23 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 07 04:26:11 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 07 04:29:59 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 07 04:33:56 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 07 04:37:43 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 07 04:41:22 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 07 04:44:59 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 07 04:48:48 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 07 04:52:53 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 07 04:56:57 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 07 05:01:00 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 07 05:04:40 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 07 05:08:27 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 07 05:12:05 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 07 05:15:43 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 07 05:19:47 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 07 05:23:28 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 07 05:27:12 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 07 05:31:01 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 07 05:34:51 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 07 05:38:46 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 07 05:42:35 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 07 05:46:14 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 07 05:50:09 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 07 05:53:45 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 07 05:57:46 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 07 06:01:32 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 07 06:05:20 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 07 06:09:02 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 07 06:12:57 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 07 06:16:40 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 07 06:20:24 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 07 06:24:12 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 07 06:27:56 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 07 06:31:36 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 07 06:35:23 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 07 06:39:06 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 07 06:43:00 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 07 06:46:49 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 07 06:50:44 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 07 06:54:27 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 07 06:58:17 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 07 07:01:59 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 07 07:05:40 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 07 07:09:16 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 07 07:12:53 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 07 07:16:41 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 07 13:56:47 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 07 14:00:07 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 07 14:01:35 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 07 14:03:19 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 07 14:05:44 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 07 14:09:06 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 07 14:14:13 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 07 14:17:04 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 07 14:19:56 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 07 14:21:19 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 07 14:22:47 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 07 14:24:37 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 07 14:26:23 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 07 14:28:12 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 07 14:29:56 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 07 14:31:40 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 07 14:33:18 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 07 14:34:34 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 07 14:35:45 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 07 14:37:22 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 07 14:39:26 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 07 14:41:23 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 07 14:43:10 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 07 14:44:57 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 07 14:47:24 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 07 14:48:55 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 07 14:50:46 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 07 14:52:43 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 07 14:54:39 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 07 14:56:31 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 07 14:58:21 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 07 15:00:22 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 07 15:02:00 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 07 15:03:14 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 07 15:04:30 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 07 15:06:11 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 07 15:07:55 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 07 15:09:39 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 07 15:11:28 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 07 15:13:17 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 07 15:15:14 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 07 15:16:29 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 07 15:18:05 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 07 15:20:01 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 07 15:21:45 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 07 15:23:23 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 07 15:25:09 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 07 15:26:50 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 07 15:28:34 IST 2026</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="0"/>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -1718,12 +2601,12 @@
   <dimension ref="A1:AG52"/>
   <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="8.77734375" style="3" collapsed="1"/>
-    <col min="2" max="2" width="30.44140625" style="3" customWidth="1" collapsed="1"/>
-    <col min="3" max="3" width="22.21875" style="3" customWidth="1" collapsed="1"/>
-    <col min="4" max="19" width="8.77734375" style="3" collapsed="1"/>
-    <col min="20" max="20" width="35.21875" style="3" customWidth="1" collapsed="1"/>
-    <col min="21" max="16384" width="8.77734375" style="3" collapsed="1"/>
+    <col min="1" max="1" style="3" width="8.77734375" collapsed="true"/>
+    <col min="2" max="2" customWidth="true" style="3" width="30.44140625" collapsed="true"/>
+    <col min="3" max="3" customWidth="true" style="3" width="22.21875" collapsed="true"/>
+    <col min="4" max="19" style="3" width="8.77734375" collapsed="true"/>
+    <col min="20" max="20" customWidth="true" style="3" width="35.21875" collapsed="true"/>
+    <col min="21" max="16384" style="3" width="8.77734375" collapsed="true"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:33" ht="28.8" x14ac:dyDescent="0.3">
@@ -1828,11 +2711,11 @@
       </c>
     </row>
     <row r="2" spans="1:33" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="3">
         <v>63</v>
       </c>
-      <c r="B2" t="s">
-        <v>182</v>
+      <c r="B2" t="s" s="3">
+        <v>427</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>28</v>
@@ -1895,10 +2778,10 @@
       </c>
     </row>
     <row r="3" spans="1:33" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
+      <c r="A3" t="s" s="3">
         <v>63</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" t="s" s="3">
         <v>124</v>
       </c>
       <c r="C3" s="1" t="s">
@@ -1962,10 +2845,10 @@
       </c>
     </row>
     <row r="4" spans="1:33" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
+      <c r="A4" t="s" s="3">
         <v>63</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" t="s" s="3">
         <v>125</v>
       </c>
       <c r="C4" s="1" t="s">
@@ -2029,10 +2912,10 @@
       </c>
     </row>
     <row r="5" spans="1:33" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
+      <c r="A5" t="s" s="3">
         <v>63</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" t="s" s="3">
         <v>126</v>
       </c>
       <c r="C5" s="1" t="s">
@@ -2096,10 +2979,10 @@
       </c>
     </row>
     <row r="6" spans="1:33" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
+      <c r="A6" t="s" s="3">
         <v>63</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B6" t="s" s="3">
         <v>127</v>
       </c>
       <c r="C6" s="1" t="s">
@@ -2163,10 +3046,10 @@
       </c>
     </row>
     <row r="7" spans="1:33" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
+      <c r="A7" t="s" s="3">
         <v>63</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" t="s" s="3">
         <v>128</v>
       </c>
       <c r="C7" s="1" t="s">
@@ -2230,10 +3113,10 @@
       </c>
     </row>
     <row r="8" spans="1:33" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
+      <c r="A8" t="s" s="3">
         <v>63</v>
       </c>
-      <c r="B8" t="s">
+      <c r="B8" t="s" s="3">
         <v>129</v>
       </c>
       <c r="C8" s="1" t="s">
@@ -2297,10 +3180,10 @@
       </c>
     </row>
     <row r="9" spans="1:33" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
+      <c r="A9" t="s" s="3">
         <v>63</v>
       </c>
-      <c r="B9" t="s">
+      <c r="B9" t="s" s="3">
         <v>130</v>
       </c>
       <c r="C9" s="1" t="s">
@@ -2364,10 +3247,10 @@
       </c>
     </row>
     <row r="10" spans="1:33" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
+      <c r="A10" t="s" s="3">
         <v>63</v>
       </c>
-      <c r="B10" t="s">
+      <c r="B10" t="s" s="3">
         <v>131</v>
       </c>
       <c r="C10" s="1" t="s">
@@ -2431,10 +3314,10 @@
       </c>
     </row>
     <row r="11" spans="1:33" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A11" t="s">
+      <c r="A11" t="s" s="3">
         <v>63</v>
       </c>
-      <c r="B11" t="s">
+      <c r="B11" t="s" s="3">
         <v>132</v>
       </c>
       <c r="C11" s="1" t="s">
@@ -2498,10 +3381,10 @@
       </c>
     </row>
     <row r="12" spans="1:33" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A12" t="s">
+      <c r="A12" t="s" s="3">
         <v>63</v>
       </c>
-      <c r="B12" t="s">
+      <c r="B12" t="s" s="3">
         <v>133</v>
       </c>
       <c r="C12" s="1" t="s">
@@ -2565,10 +3448,10 @@
       </c>
     </row>
     <row r="13" spans="1:33" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A13" t="s">
+      <c r="A13" t="s" s="3">
         <v>63</v>
       </c>
-      <c r="B13" t="s">
+      <c r="B13" t="s" s="3">
         <v>134</v>
       </c>
       <c r="C13" s="1" t="s">
@@ -2632,10 +3515,10 @@
       </c>
     </row>
     <row r="14" spans="1:33" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A14" t="s">
+      <c r="A14" t="s" s="3">
         <v>63</v>
       </c>
-      <c r="B14" t="s">
+      <c r="B14" t="s" s="3">
         <v>135</v>
       </c>
       <c r="C14" s="1" t="s">
@@ -2699,10 +3582,10 @@
       </c>
     </row>
     <row r="15" spans="1:33" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A15" t="s">
+      <c r="A15" t="s" s="3">
         <v>63</v>
       </c>
-      <c r="B15" t="s">
+      <c r="B15" t="s" s="3">
         <v>136</v>
       </c>
       <c r="C15" s="1" t="s">
@@ -2766,10 +3649,10 @@
       </c>
     </row>
     <row r="16" spans="1:33" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A16" t="s">
+      <c r="A16" t="s" s="3">
         <v>63</v>
       </c>
-      <c r="B16" t="s">
+      <c r="B16" t="s" s="3">
         <v>137</v>
       </c>
       <c r="C16" s="1" t="s">
@@ -2833,10 +3716,10 @@
       </c>
     </row>
     <row r="17" spans="1:33" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A17" t="s">
+      <c r="A17" t="s" s="3">
         <v>63</v>
       </c>
-      <c r="B17" t="s">
+      <c r="B17" t="s" s="3">
         <v>138</v>
       </c>
       <c r="C17" s="1" t="s">
@@ -2900,10 +3783,10 @@
       </c>
     </row>
     <row r="18" spans="1:33" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A18" t="s">
+      <c r="A18" t="s" s="3">
         <v>63</v>
       </c>
-      <c r="B18" t="s">
+      <c r="B18" t="s" s="3">
         <v>139</v>
       </c>
       <c r="C18" s="1" t="s">
@@ -2967,10 +3850,10 @@
       </c>
     </row>
     <row r="19" spans="1:33" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A19" t="s">
+      <c r="A19" t="s" s="3">
         <v>63</v>
       </c>
-      <c r="B19" t="s">
+      <c r="B19" t="s" s="3">
         <v>140</v>
       </c>
       <c r="C19" s="1" t="s">
@@ -3034,10 +3917,10 @@
       </c>
     </row>
     <row r="20" spans="1:33" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A20" t="s">
+      <c r="A20" t="s" s="3">
         <v>63</v>
       </c>
-      <c r="B20" t="s">
+      <c r="B20" t="s" s="3">
         <v>141</v>
       </c>
       <c r="C20" s="1" t="s">
@@ -3101,10 +3984,10 @@
       </c>
     </row>
     <row r="21" spans="1:33" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A21" t="s">
+      <c r="A21" t="s" s="3">
         <v>63</v>
       </c>
-      <c r="B21" t="s">
+      <c r="B21" t="s" s="3">
         <v>142</v>
       </c>
       <c r="C21" s="1" t="s">
@@ -3168,10 +4051,10 @@
       </c>
     </row>
     <row r="22" spans="1:33" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A22" t="s">
+      <c r="A22" t="s" s="3">
         <v>63</v>
       </c>
-      <c r="B22" t="s">
+      <c r="B22" t="s" s="3">
         <v>143</v>
       </c>
       <c r="C22" s="1" t="s">
@@ -3235,10 +4118,10 @@
       </c>
     </row>
     <row r="23" spans="1:33" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A23" t="s">
+      <c r="A23" t="s" s="3">
         <v>63</v>
       </c>
-      <c r="B23" t="s">
+      <c r="B23" t="s" s="3">
         <v>144</v>
       </c>
       <c r="C23" s="1" t="s">
@@ -3302,10 +4185,10 @@
       </c>
     </row>
     <row r="24" spans="1:33" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A24" t="s">
+      <c r="A24" t="s" s="3">
         <v>63</v>
       </c>
-      <c r="B24" t="s">
+      <c r="B24" t="s" s="3">
         <v>145</v>
       </c>
       <c r="C24" s="1" t="s">
@@ -3369,10 +4252,10 @@
       </c>
     </row>
     <row r="25" spans="1:33" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A25" t="s">
+      <c r="A25" t="s" s="3">
         <v>63</v>
       </c>
-      <c r="B25" t="s">
+      <c r="B25" t="s" s="3">
         <v>146</v>
       </c>
       <c r="C25" s="1" t="s">
@@ -3436,10 +4319,10 @@
       </c>
     </row>
     <row r="26" spans="1:33" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A26" t="s">
+      <c r="A26" t="s" s="3">
         <v>63</v>
       </c>
-      <c r="B26" t="s">
+      <c r="B26" t="s" s="3">
         <v>147</v>
       </c>
       <c r="C26" s="1" t="s">
@@ -3503,10 +4386,10 @@
       </c>
     </row>
     <row r="27" spans="1:33" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A27" t="s">
+      <c r="A27" t="s" s="3">
         <v>63</v>
       </c>
-      <c r="B27" t="s">
+      <c r="B27" t="s" s="3">
         <v>148</v>
       </c>
       <c r="C27" s="1" t="s">
@@ -3570,10 +4453,10 @@
       </c>
     </row>
     <row r="28" spans="1:33" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A28" t="s">
+      <c r="A28" t="s" s="3">
         <v>63</v>
       </c>
-      <c r="B28" t="s">
+      <c r="B28" t="s" s="3">
         <v>149</v>
       </c>
       <c r="C28" s="1" t="s">
@@ -3637,10 +4520,10 @@
       </c>
     </row>
     <row r="29" spans="1:33" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A29" t="s">
+      <c r="A29" t="s" s="3">
         <v>63</v>
       </c>
-      <c r="B29" t="s">
+      <c r="B29" t="s" s="3">
         <v>150</v>
       </c>
       <c r="C29" s="1" t="s">
@@ -3704,10 +4587,10 @@
       </c>
     </row>
     <row r="30" spans="1:33" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A30" t="s">
+      <c r="A30" t="s" s="3">
         <v>63</v>
       </c>
-      <c r="B30" t="s">
+      <c r="B30" t="s" s="3">
         <v>151</v>
       </c>
       <c r="C30" s="1" t="s">
@@ -3771,10 +4654,10 @@
       </c>
     </row>
     <row r="31" spans="1:33" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A31" t="s">
+      <c r="A31" t="s" s="3">
         <v>63</v>
       </c>
-      <c r="B31" t="s">
+      <c r="B31" t="s" s="3">
         <v>152</v>
       </c>
       <c r="C31" s="1" t="s">
@@ -3838,10 +4721,10 @@
       </c>
     </row>
     <row r="32" spans="1:33" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A32" t="s">
+      <c r="A32" t="s" s="3">
         <v>63</v>
       </c>
-      <c r="B32" t="s">
+      <c r="B32" t="s" s="3">
         <v>153</v>
       </c>
       <c r="C32" s="1" t="s">
@@ -3905,10 +4788,10 @@
       </c>
     </row>
     <row r="33" spans="1:33" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A33" t="s">
+      <c r="A33" t="s" s="3">
         <v>63</v>
       </c>
-      <c r="B33" t="s">
+      <c r="B33" t="s" s="3">
         <v>154</v>
       </c>
       <c r="C33" s="1" t="s">
@@ -3972,10 +4855,10 @@
       </c>
     </row>
     <row r="34" spans="1:33" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A34" t="s">
+      <c r="A34" t="s" s="3">
         <v>63</v>
       </c>
-      <c r="B34" t="s">
+      <c r="B34" t="s" s="3">
         <v>155</v>
       </c>
       <c r="C34" s="1" t="s">
@@ -4039,10 +4922,10 @@
       </c>
     </row>
     <row r="35" spans="1:33" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A35" t="s">
+      <c r="A35" t="s" s="3">
         <v>63</v>
       </c>
-      <c r="B35" t="s">
+      <c r="B35" t="s" s="3">
         <v>156</v>
       </c>
       <c r="C35" s="1" t="s">
@@ -4106,10 +4989,10 @@
       </c>
     </row>
     <row r="36" spans="1:33" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A36" t="s">
+      <c r="A36" t="s" s="3">
         <v>63</v>
       </c>
-      <c r="B36" t="s">
+      <c r="B36" t="s" s="3">
         <v>157</v>
       </c>
       <c r="C36" s="1" t="s">
@@ -4173,10 +5056,10 @@
       </c>
     </row>
     <row r="37" spans="1:33" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A37" t="s">
+      <c r="A37" t="s" s="3">
         <v>63</v>
       </c>
-      <c r="B37" t="s">
+      <c r="B37" t="s" s="3">
         <v>158</v>
       </c>
       <c r="C37" s="1" t="s">
@@ -4240,10 +5123,10 @@
       </c>
     </row>
     <row r="38" spans="1:33" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A38" t="s">
+      <c r="A38" t="s" s="3">
         <v>63</v>
       </c>
-      <c r="B38" t="s">
+      <c r="B38" t="s" s="3">
         <v>159</v>
       </c>
       <c r="C38" s="1" t="s">
@@ -4307,10 +5190,10 @@
       </c>
     </row>
     <row r="39" spans="1:33" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A39" t="s">
+      <c r="A39" t="s" s="3">
         <v>63</v>
       </c>
-      <c r="B39" t="s">
+      <c r="B39" t="s" s="3">
         <v>160</v>
       </c>
       <c r="C39" s="1" t="s">
@@ -4374,10 +5257,10 @@
       </c>
     </row>
     <row r="40" spans="1:33" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A40" t="s">
+      <c r="A40" t="s" s="3">
         <v>63</v>
       </c>
-      <c r="B40" t="s">
+      <c r="B40" t="s" s="3">
         <v>161</v>
       </c>
       <c r="C40" s="1" t="s">
@@ -4441,10 +5324,10 @@
       </c>
     </row>
     <row r="41" spans="1:33" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A41" t="s">
+      <c r="A41" t="s" s="3">
         <v>63</v>
       </c>
-      <c r="B41" t="s">
+      <c r="B41" t="s" s="3">
         <v>162</v>
       </c>
       <c r="C41" s="1" t="s">
@@ -4508,10 +5391,10 @@
       </c>
     </row>
     <row r="42" spans="1:33" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A42" t="s">
+      <c r="A42" t="s" s="3">
         <v>63</v>
       </c>
-      <c r="B42" t="s">
+      <c r="B42" t="s" s="3">
         <v>163</v>
       </c>
       <c r="C42" s="1" t="s">
@@ -4575,10 +5458,10 @@
       </c>
     </row>
     <row r="43" spans="1:33" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A43" t="s">
+      <c r="A43" t="s" s="3">
         <v>63</v>
       </c>
-      <c r="B43" t="s">
+      <c r="B43" t="s" s="3">
         <v>164</v>
       </c>
       <c r="C43" s="1" t="s">
@@ -4642,10 +5525,10 @@
       </c>
     </row>
     <row r="44" spans="1:33" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A44" t="s">
+      <c r="A44" t="s" s="3">
         <v>63</v>
       </c>
-      <c r="B44" t="s">
+      <c r="B44" t="s" s="3">
         <v>165</v>
       </c>
       <c r="C44" s="1" t="s">
@@ -4709,10 +5592,10 @@
       </c>
     </row>
     <row r="45" spans="1:33" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A45" t="s">
+      <c r="A45" t="s" s="3">
         <v>63</v>
       </c>
-      <c r="B45" t="s">
+      <c r="B45" t="s" s="3">
         <v>166</v>
       </c>
       <c r="C45" s="1" t="s">
@@ -4776,10 +5659,10 @@
       </c>
     </row>
     <row r="46" spans="1:33" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A46" t="s">
+      <c r="A46" t="s" s="3">
         <v>63</v>
       </c>
-      <c r="B46" t="s">
+      <c r="B46" t="s" s="3">
         <v>167</v>
       </c>
       <c r="C46" s="1" t="s">
@@ -4843,10 +5726,10 @@
       </c>
     </row>
     <row r="47" spans="1:33" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A47" t="s">
+      <c r="A47" t="s" s="3">
         <v>63</v>
       </c>
-      <c r="B47" t="s">
+      <c r="B47" t="s" s="3">
         <v>168</v>
       </c>
       <c r="C47" s="1" t="s">
@@ -4910,10 +5793,10 @@
       </c>
     </row>
     <row r="48" spans="1:33" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A48" t="s">
+      <c r="A48" t="s" s="3">
         <v>63</v>
       </c>
-      <c r="B48" t="s">
+      <c r="B48" t="s" s="3">
         <v>169</v>
       </c>
       <c r="C48" s="1" t="s">
@@ -4977,10 +5860,10 @@
       </c>
     </row>
     <row r="49" spans="1:33" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A49" t="s">
+      <c r="A49" t="s" s="3">
         <v>63</v>
       </c>
-      <c r="B49" t="s">
+      <c r="B49" t="s" s="3">
         <v>170</v>
       </c>
       <c r="C49" s="1" t="s">
@@ -5044,10 +5927,10 @@
       </c>
     </row>
     <row r="50" spans="1:33" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A50" t="s">
+      <c r="A50" t="s" s="3">
         <v>63</v>
       </c>
-      <c r="B50" t="s">
+      <c r="B50" t="s" s="3">
         <v>171</v>
       </c>
       <c r="C50" s="1" t="s">
@@ -5111,10 +5994,10 @@
       </c>
     </row>
     <row r="51" spans="1:33" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A51" t="s">
+      <c r="A51" t="s" s="3">
         <v>63</v>
       </c>
-      <c r="B51" t="s">
+      <c r="B51" t="s" s="3">
         <v>172</v>
       </c>
       <c r="C51" s="1" t="s">
@@ -5178,10 +6061,10 @@
       </c>
     </row>
     <row r="52" spans="1:33" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A52" t="s">
+      <c r="A52" t="s" s="3">
         <v>63</v>
       </c>
-      <c r="B52" t="s">
+      <c r="B52" t="s" s="3">
         <v>173</v>
       </c>
       <c r="C52" s="1" t="s">
@@ -5258,9 +6141,9 @@
   <dimension ref="A1:AH52"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="21" max="21" width="10" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="30" max="30" width="8.77734375" style="3" collapsed="1"/>
-    <col min="32" max="33" width="9" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="21" max="21" bestFit="true" customWidth="true" width="10.0" collapsed="true"/>
+    <col min="30" max="30" style="3" width="8.77734375" collapsed="true"/>
+    <col min="32" max="33" bestFit="true" customWidth="true" width="9.0" collapsed="true"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:34" ht="28.8" x14ac:dyDescent="0.3">
@@ -5368,10 +6251,10 @@
       </c>
     </row>
     <row r="2" spans="1:34" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>63</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" t="s" s="0">
         <v>178</v>
       </c>
       <c r="C2" s="1" t="s">
@@ -5436,10 +6319,10 @@
       </c>
     </row>
     <row r="3" spans="1:34" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
+      <c r="A3" t="s" s="0">
         <v>63</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" t="s" s="0">
         <v>179</v>
       </c>
       <c r="C3" s="1" t="s">
@@ -5504,10 +6387,10 @@
       </c>
     </row>
     <row r="4" spans="1:34" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
+      <c r="A4" t="s" s="0">
         <v>63</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" t="s" s="0">
         <v>181</v>
       </c>
       <c r="C4" s="1" t="s">
@@ -5572,11 +6455,11 @@
       </c>
     </row>
     <row r="5" spans="1:34" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>63</v>
-      </c>
-      <c r="B5" t="s">
-        <v>367</v>
+      <c r="A5" t="s" s="0">
+        <v>177</v>
+      </c>
+      <c r="B5" t="s" s="0">
+        <v>612</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>42</v>
@@ -5640,11 +6523,11 @@
       </c>
     </row>
     <row r="6" spans="1:34" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
-        <v>63</v>
-      </c>
-      <c r="B6" t="s">
-        <v>368</v>
+      <c r="A6" t="s" s="0">
+        <v>177</v>
+      </c>
+      <c r="B6" t="s" s="0">
+        <v>613</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>42</v>
@@ -5708,11 +6591,11 @@
       </c>
     </row>
     <row r="7" spans="1:34" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
-        <v>63</v>
-      </c>
-      <c r="B7" t="s">
-        <v>369</v>
+      <c r="A7" t="s" s="0">
+        <v>177</v>
+      </c>
+      <c r="B7" t="s" s="0">
+        <v>614</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>42</v>
@@ -5776,11 +6659,11 @@
       </c>
     </row>
     <row r="8" spans="1:34" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
-        <v>63</v>
-      </c>
-      <c r="B8" t="s">
-        <v>370</v>
+      <c r="A8" t="s" s="0">
+        <v>177</v>
+      </c>
+      <c r="B8" t="s" s="0">
+        <v>615</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>42</v>
@@ -5844,11 +6727,11 @@
       </c>
     </row>
     <row r="9" spans="1:34" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
-        <v>63</v>
-      </c>
-      <c r="B9" t="s">
-        <v>371</v>
+      <c r="A9" t="s" s="0">
+        <v>177</v>
+      </c>
+      <c r="B9" t="s" s="0">
+        <v>616</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>42</v>
@@ -5912,11 +6795,11 @@
       </c>
     </row>
     <row r="10" spans="1:34" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
-        <v>63</v>
-      </c>
-      <c r="B10" t="s">
-        <v>372</v>
+      <c r="A10" t="s" s="0">
+        <v>177</v>
+      </c>
+      <c r="B10" t="s" s="0">
+        <v>617</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>42</v>
@@ -6116,9 +6999,9 @@
   <dimension ref="A1:AH52"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="21" max="21" width="10" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="30" max="30" width="8.77734375" style="3" collapsed="1"/>
-    <col min="32" max="33" width="9" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="21" max="21" bestFit="true" customWidth="true" width="10.0" collapsed="true"/>
+    <col min="30" max="30" style="3" width="8.77734375" collapsed="true"/>
+    <col min="32" max="33" bestFit="true" customWidth="true" width="9.0" collapsed="true"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:34" ht="28.8" x14ac:dyDescent="0.3">
@@ -6226,11 +7109,11 @@
       </c>
     </row>
     <row r="2" spans="1:34" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>63</v>
-      </c>
-      <c r="B2" t="s">
-        <v>373</v>
+      <c r="A2" t="s" s="0">
+        <v>177</v>
+      </c>
+      <c r="B2" t="s" s="0">
+        <v>618</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>42</v>
@@ -6294,11 +7177,11 @@
       </c>
     </row>
     <row r="3" spans="1:34" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>63</v>
-      </c>
-      <c r="B3" t="s">
-        <v>374</v>
+      <c r="A3" t="s" s="0">
+        <v>177</v>
+      </c>
+      <c r="B3" t="s" s="0">
+        <v>619</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>42</v>
@@ -6362,11 +7245,11 @@
       </c>
     </row>
     <row r="4" spans="1:34" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>63</v>
-      </c>
-      <c r="B4" t="s">
-        <v>375</v>
+      <c r="A4" t="s" s="0">
+        <v>177</v>
+      </c>
+      <c r="B4" t="s" s="0">
+        <v>620</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>42</v>
@@ -6430,11 +7313,11 @@
       </c>
     </row>
     <row r="5" spans="1:34" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>63</v>
-      </c>
-      <c r="B5" t="s">
-        <v>376</v>
+      <c r="A5" t="s" s="0">
+        <v>177</v>
+      </c>
+      <c r="B5" t="s" s="0">
+        <v>621</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>42</v>
@@ -6498,11 +7381,11 @@
       </c>
     </row>
     <row r="6" spans="1:34" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
-        <v>63</v>
-      </c>
-      <c r="B6" t="s">
-        <v>377</v>
+      <c r="A6" t="s" s="0">
+        <v>177</v>
+      </c>
+      <c r="B6" t="s" s="0">
+        <v>622</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>42</v>
@@ -6566,11 +7449,11 @@
       </c>
     </row>
     <row r="7" spans="1:34" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
-        <v>63</v>
-      </c>
-      <c r="B7" t="s">
-        <v>378</v>
+      <c r="A7" t="s" s="0">
+        <v>177</v>
+      </c>
+      <c r="B7" t="s" s="0">
+        <v>623</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>42</v>
@@ -6634,11 +7517,11 @@
       </c>
     </row>
     <row r="8" spans="1:34" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
-        <v>63</v>
-      </c>
-      <c r="B8" t="s">
-        <v>379</v>
+      <c r="A8" t="s" s="0">
+        <v>177</v>
+      </c>
+      <c r="B8" t="s" s="0">
+        <v>624</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>42</v>
@@ -6702,11 +7585,11 @@
       </c>
     </row>
     <row r="9" spans="1:34" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
-        <v>63</v>
-      </c>
-      <c r="B9" t="s">
-        <v>380</v>
+      <c r="A9" t="s" s="0">
+        <v>177</v>
+      </c>
+      <c r="B9" t="s" s="0">
+        <v>625</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>42</v>
@@ -6770,11 +7653,11 @@
       </c>
     </row>
     <row r="10" spans="1:34" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
-        <v>63</v>
-      </c>
-      <c r="B10" t="s">
-        <v>381</v>
+      <c r="A10" t="s" s="0">
+        <v>177</v>
+      </c>
+      <c r="B10" t="s" s="0">
+        <v>626</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>42</v>
@@ -6973,9 +7856,9 @@
   <dimension ref="A1:AH52"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="21" max="21" width="10" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="30" max="30" width="8.77734375" style="3" collapsed="1"/>
-    <col min="32" max="33" width="9" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="21" max="21" bestFit="true" customWidth="true" width="10.0" collapsed="true"/>
+    <col min="30" max="30" style="3" width="8.77734375" collapsed="true"/>
+    <col min="32" max="33" bestFit="true" customWidth="true" width="9.0" collapsed="true"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:34" ht="28.8" x14ac:dyDescent="0.3">
@@ -7083,11 +7966,11 @@
       </c>
     </row>
     <row r="2" spans="1:34" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>63</v>
-      </c>
-      <c r="B2" t="s">
-        <v>382</v>
+      <c r="A2" t="s" s="0">
+        <v>177</v>
+      </c>
+      <c r="B2" t="s" s="0">
+        <v>627</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>42</v>
@@ -7151,11 +8034,11 @@
       </c>
     </row>
     <row r="3" spans="1:34" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>63</v>
-      </c>
-      <c r="B3" t="s">
-        <v>383</v>
+      <c r="A3" t="s" s="0">
+        <v>177</v>
+      </c>
+      <c r="B3" t="s" s="0">
+        <v>628</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>42</v>
@@ -7219,11 +8102,11 @@
       </c>
     </row>
     <row r="4" spans="1:34" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>63</v>
-      </c>
-      <c r="B4" t="s">
-        <v>384</v>
+      <c r="A4" t="s" s="0">
+        <v>177</v>
+      </c>
+      <c r="B4" t="s" s="0">
+        <v>629</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>42</v>
@@ -7287,11 +8170,11 @@
       </c>
     </row>
     <row r="5" spans="1:34" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>63</v>
-      </c>
-      <c r="B5" t="s">
-        <v>385</v>
+      <c r="A5" t="s" s="0">
+        <v>177</v>
+      </c>
+      <c r="B5" t="s" s="0">
+        <v>630</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>42</v>
@@ -7355,11 +8238,11 @@
       </c>
     </row>
     <row r="6" spans="1:34" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
-        <v>63</v>
-      </c>
-      <c r="B6" t="s">
-        <v>386</v>
+      <c r="A6" t="s" s="0">
+        <v>177</v>
+      </c>
+      <c r="B6" t="s" s="0">
+        <v>631</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>42</v>
@@ -7423,11 +8306,11 @@
       </c>
     </row>
     <row r="7" spans="1:34" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
-        <v>63</v>
-      </c>
-      <c r="B7" t="s">
-        <v>387</v>
+      <c r="A7" t="s" s="0">
+        <v>177</v>
+      </c>
+      <c r="B7" t="s" s="0">
+        <v>632</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>42</v>
@@ -7491,11 +8374,11 @@
       </c>
     </row>
     <row r="8" spans="1:34" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
-        <v>63</v>
-      </c>
-      <c r="B8" t="s">
-        <v>388</v>
+      <c r="A8" t="s" s="0">
+        <v>177</v>
+      </c>
+      <c r="B8" t="s" s="0">
+        <v>633</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>42</v>
@@ -7559,11 +8442,11 @@
       </c>
     </row>
     <row r="9" spans="1:34" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
-        <v>63</v>
-      </c>
-      <c r="B9" t="s">
-        <v>389</v>
+      <c r="A9" t="s" s="0">
+        <v>177</v>
+      </c>
+      <c r="B9" t="s" s="0">
+        <v>634</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>42</v>
@@ -7627,11 +8510,11 @@
       </c>
     </row>
     <row r="10" spans="1:34" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
-        <v>63</v>
-      </c>
-      <c r="B10" t="s">
-        <v>390</v>
+      <c r="A10" t="s" s="0">
+        <v>177</v>
+      </c>
+      <c r="B10" t="s" s="0">
+        <v>635</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>42</v>
@@ -7830,13 +8713,13 @@
   <dimension ref="A1:AI52"/>
   <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="8.77734375" style="3" collapsed="1"/>
-    <col min="2" max="2" width="16.77734375" style="3" customWidth="1" collapsed="1"/>
-    <col min="3" max="20" width="8.77734375" style="3" collapsed="1"/>
-    <col min="21" max="21" width="10" style="3" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="22" max="31" width="8.77734375" style="3" collapsed="1"/>
-    <col min="32" max="33" width="9" style="3" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="34" max="16384" width="8.77734375" style="3" collapsed="1"/>
+    <col min="1" max="1" style="3" width="8.77734375" collapsed="true"/>
+    <col min="2" max="2" customWidth="true" style="3" width="16.77734375" collapsed="true"/>
+    <col min="3" max="20" style="3" width="8.77734375" collapsed="true"/>
+    <col min="21" max="21" bestFit="true" customWidth="true" style="3" width="10.0" collapsed="true"/>
+    <col min="22" max="31" style="3" width="8.77734375" collapsed="true"/>
+    <col min="32" max="33" bestFit="true" customWidth="true" style="3" width="9.0" collapsed="true"/>
+    <col min="34" max="16384" style="3" width="8.77734375" collapsed="true"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:35" ht="28.8" x14ac:dyDescent="0.3">
@@ -7945,11 +8828,11 @@
       <c r="AI1" s="4"/>
     </row>
     <row r="2" spans="1:35" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>63</v>
-      </c>
-      <c r="B2" t="s">
-        <v>391</v>
+      <c r="A2" t="s" s="3">
+        <v>177</v>
+      </c>
+      <c r="B2" t="s" s="3">
+        <v>636</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>42</v>
@@ -8013,11 +8896,11 @@
       </c>
     </row>
     <row r="3" spans="1:35" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>63</v>
-      </c>
-      <c r="B3" t="s">
-        <v>392</v>
+      <c r="A3" t="s" s="3">
+        <v>177</v>
+      </c>
+      <c r="B3" t="s" s="3">
+        <v>637</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>42</v>
@@ -8081,11 +8964,11 @@
       </c>
     </row>
     <row r="4" spans="1:35" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>63</v>
-      </c>
-      <c r="B4" t="s">
-        <v>393</v>
+      <c r="A4" t="s" s="3">
+        <v>177</v>
+      </c>
+      <c r="B4" t="s" s="3">
+        <v>638</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>42</v>
@@ -8149,11 +9032,11 @@
       </c>
     </row>
     <row r="5" spans="1:35" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>63</v>
-      </c>
-      <c r="B5" t="s">
-        <v>394</v>
+      <c r="A5" t="s" s="3">
+        <v>177</v>
+      </c>
+      <c r="B5" t="s" s="3">
+        <v>639</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>42</v>
@@ -8217,11 +9100,11 @@
       </c>
     </row>
     <row r="6" spans="1:35" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
-        <v>63</v>
-      </c>
-      <c r="B6" t="s">
-        <v>395</v>
+      <c r="A6" t="s" s="3">
+        <v>177</v>
+      </c>
+      <c r="B6" t="s" s="3">
+        <v>640</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>42</v>
@@ -8285,11 +9168,11 @@
       </c>
     </row>
     <row r="7" spans="1:35" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
-        <v>63</v>
-      </c>
-      <c r="B7" t="s">
-        <v>396</v>
+      <c r="A7" t="s" s="3">
+        <v>177</v>
+      </c>
+      <c r="B7" t="s" s="3">
+        <v>641</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>42</v>
@@ -8353,11 +9236,11 @@
       </c>
     </row>
     <row r="8" spans="1:35" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
-        <v>63</v>
-      </c>
-      <c r="B8" t="s">
-        <v>397</v>
+      <c r="A8" t="s" s="3">
+        <v>177</v>
+      </c>
+      <c r="B8" t="s" s="3">
+        <v>642</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>42</v>
@@ -8421,11 +9304,11 @@
       </c>
     </row>
     <row r="9" spans="1:35" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
-        <v>63</v>
-      </c>
-      <c r="B9" t="s">
-        <v>398</v>
+      <c r="A9" t="s" s="3">
+        <v>177</v>
+      </c>
+      <c r="B9" t="s" s="3">
+        <v>643</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>42</v>
@@ -8489,11 +9372,11 @@
       </c>
     </row>
     <row r="10" spans="1:35" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
-        <v>63</v>
-      </c>
-      <c r="B10" t="s">
-        <v>399</v>
+      <c r="A10" t="s" s="3">
+        <v>177</v>
+      </c>
+      <c r="B10" t="s" s="3">
+        <v>644</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>42</v>
@@ -8692,13 +9575,13 @@
   <dimension ref="A1:AH52"/>
   <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="8.77734375" style="3" collapsed="1"/>
-    <col min="2" max="2" width="28.21875" style="3" customWidth="1" collapsed="1"/>
-    <col min="3" max="20" width="8.77734375" style="3" collapsed="1"/>
-    <col min="21" max="21" width="10" style="3" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="22" max="31" width="8.77734375" style="3" collapsed="1"/>
-    <col min="32" max="33" width="9" style="3" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="34" max="16384" width="8.77734375" style="3" collapsed="1"/>
+    <col min="1" max="1" style="3" width="8.77734375" collapsed="true"/>
+    <col min="2" max="2" customWidth="true" style="3" width="28.21875" collapsed="true"/>
+    <col min="3" max="20" style="3" width="8.77734375" collapsed="true"/>
+    <col min="21" max="21" bestFit="true" customWidth="true" style="3" width="10.0" collapsed="true"/>
+    <col min="22" max="31" style="3" width="8.77734375" collapsed="true"/>
+    <col min="32" max="33" bestFit="true" customWidth="true" style="3" width="9.0" collapsed="true"/>
+    <col min="34" max="16384" style="3" width="8.77734375" collapsed="true"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:34" ht="28.8" x14ac:dyDescent="0.3">
@@ -8806,11 +9689,11 @@
       </c>
     </row>
     <row r="2" spans="1:34" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>63</v>
-      </c>
-      <c r="B2" t="s">
-        <v>400</v>
+      <c r="A2" t="s" s="3">
+        <v>177</v>
+      </c>
+      <c r="B2" t="s" s="3">
+        <v>645</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>42</v>
@@ -8874,11 +9757,11 @@
       </c>
     </row>
     <row r="3" spans="1:34" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>63</v>
-      </c>
-      <c r="B3" t="s">
-        <v>401</v>
+      <c r="A3" t="s" s="3">
+        <v>177</v>
+      </c>
+      <c r="B3" t="s" s="3">
+        <v>646</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>42</v>
@@ -8942,11 +9825,11 @@
       </c>
     </row>
     <row r="4" spans="1:34" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>63</v>
-      </c>
-      <c r="B4" t="s">
-        <v>402</v>
+      <c r="A4" t="s" s="3">
+        <v>177</v>
+      </c>
+      <c r="B4" t="s" s="3">
+        <v>647</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>42</v>
@@ -9010,11 +9893,11 @@
       </c>
     </row>
     <row r="5" spans="1:34" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>63</v>
-      </c>
-      <c r="B5" t="s">
-        <v>403</v>
+      <c r="A5" t="s" s="3">
+        <v>177</v>
+      </c>
+      <c r="B5" t="s" s="3">
+        <v>648</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>42</v>
@@ -9078,11 +9961,11 @@
       </c>
     </row>
     <row r="6" spans="1:34" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
-        <v>63</v>
-      </c>
-      <c r="B6" t="s">
-        <v>404</v>
+      <c r="A6" t="s" s="3">
+        <v>177</v>
+      </c>
+      <c r="B6" t="s" s="3">
+        <v>649</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>42</v>
@@ -9146,11 +10029,11 @@
       </c>
     </row>
     <row r="7" spans="1:34" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
-        <v>63</v>
-      </c>
-      <c r="B7" t="s">
-        <v>405</v>
+      <c r="A7" t="s" s="3">
+        <v>177</v>
+      </c>
+      <c r="B7" t="s" s="3">
+        <v>650</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>42</v>
@@ -9214,11 +10097,11 @@
       </c>
     </row>
     <row r="8" spans="1:34" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
-        <v>63</v>
-      </c>
-      <c r="B8" t="s">
-        <v>406</v>
+      <c r="A8" t="s" s="3">
+        <v>177</v>
+      </c>
+      <c r="B8" t="s" s="3">
+        <v>651</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>42</v>
@@ -9282,11 +10165,11 @@
       </c>
     </row>
     <row r="9" spans="1:34" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
-        <v>63</v>
-      </c>
-      <c r="B9" t="s">
-        <v>407</v>
+      <c r="A9" t="s" s="3">
+        <v>177</v>
+      </c>
+      <c r="B9" t="s" s="3">
+        <v>652</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>42</v>
@@ -9350,11 +10233,11 @@
       </c>
     </row>
     <row r="10" spans="1:34" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
-        <v>63</v>
-      </c>
-      <c r="B10" t="s">
-        <v>408</v>
+      <c r="A10" t="s" s="3">
+        <v>177</v>
+      </c>
+      <c r="B10" t="s" s="3">
+        <v>653</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>42</v>
@@ -9553,9 +10436,9 @@
   <dimension ref="A1:AH52"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="21" max="21" width="10" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="30" max="30" width="8.77734375" style="3" collapsed="1"/>
-    <col min="32" max="33" width="9" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="21" max="21" bestFit="true" customWidth="true" width="10.0" collapsed="true"/>
+    <col min="30" max="30" style="3" width="8.77734375" collapsed="true"/>
+    <col min="32" max="33" bestFit="true" customWidth="true" width="9.0" collapsed="true"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:34" ht="28.8" x14ac:dyDescent="0.3">
@@ -9663,11 +10546,11 @@
       </c>
     </row>
     <row r="2" spans="1:34" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>63</v>
-      </c>
-      <c r="B2" t="s">
-        <v>409</v>
+      <c r="A2" t="s" s="0">
+        <v>177</v>
+      </c>
+      <c r="B2" t="s" s="0">
+        <v>654</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>42</v>
@@ -9731,11 +10614,11 @@
       </c>
     </row>
     <row r="3" spans="1:34" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>63</v>
-      </c>
-      <c r="B3" t="s">
-        <v>410</v>
+      <c r="A3" t="s" s="0">
+        <v>177</v>
+      </c>
+      <c r="B3" t="s" s="0">
+        <v>655</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>42</v>
@@ -9799,11 +10682,11 @@
       </c>
     </row>
     <row r="4" spans="1:34" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>63</v>
-      </c>
-      <c r="B4" t="s">
-        <v>411</v>
+      <c r="A4" t="s" s="0">
+        <v>177</v>
+      </c>
+      <c r="B4" t="s" s="0">
+        <v>656</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>42</v>
@@ -9867,11 +10750,11 @@
       </c>
     </row>
     <row r="5" spans="1:34" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>63</v>
-      </c>
-      <c r="B5" t="s">
-        <v>412</v>
+      <c r="A5" t="s" s="0">
+        <v>177</v>
+      </c>
+      <c r="B5" t="s" s="0">
+        <v>657</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>42</v>
@@ -9935,11 +10818,11 @@
       </c>
     </row>
     <row r="6" spans="1:34" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
-        <v>63</v>
-      </c>
-      <c r="B6" t="s">
-        <v>413</v>
+      <c r="A6" t="s" s="0">
+        <v>177</v>
+      </c>
+      <c r="B6" t="s" s="0">
+        <v>658</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>42</v>
@@ -10003,11 +10886,11 @@
       </c>
     </row>
     <row r="7" spans="1:34" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
-        <v>63</v>
-      </c>
-      <c r="B7" t="s">
-        <v>414</v>
+      <c r="A7" t="s" s="0">
+        <v>177</v>
+      </c>
+      <c r="B7" t="s" s="0">
+        <v>659</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>42</v>
@@ -10071,11 +10954,11 @@
       </c>
     </row>
     <row r="8" spans="1:34" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
-        <v>63</v>
-      </c>
-      <c r="B8" t="s">
-        <v>415</v>
+      <c r="A8" t="s" s="0">
+        <v>177</v>
+      </c>
+      <c r="B8" t="s" s="0">
+        <v>660</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>42</v>
@@ -10139,11 +11022,11 @@
       </c>
     </row>
     <row r="9" spans="1:34" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
-        <v>63</v>
-      </c>
-      <c r="B9" t="s">
-        <v>416</v>
+      <c r="A9" t="s" s="0">
+        <v>177</v>
+      </c>
+      <c r="B9" t="s" s="0">
+        <v>661</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>42</v>
@@ -10207,11 +11090,11 @@
       </c>
     </row>
     <row r="10" spans="1:34" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
-        <v>63</v>
-      </c>
-      <c r="B10" t="s">
-        <v>417</v>
+      <c r="A10" t="s" s="0">
+        <v>177</v>
+      </c>
+      <c r="B10" t="s" s="0">
+        <v>662</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>42</v>
@@ -10410,9 +11293,9 @@
   <dimension ref="A1:AH52"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="21" max="21" width="10" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="30" max="30" width="8.77734375" style="3" collapsed="1"/>
-    <col min="32" max="33" width="9" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="21" max="21" bestFit="true" customWidth="true" width="10.0" collapsed="true"/>
+    <col min="30" max="30" style="3" width="8.77734375" collapsed="true"/>
+    <col min="32" max="33" bestFit="true" customWidth="true" width="9.0" collapsed="true"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:34" ht="28.8" x14ac:dyDescent="0.3">
@@ -10520,11 +11403,11 @@
       </c>
     </row>
     <row r="2" spans="1:34" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>63</v>
-      </c>
-      <c r="B2" t="s">
-        <v>418</v>
+      <c r="A2" t="s" s="0">
+        <v>177</v>
+      </c>
+      <c r="B2" t="s" s="0">
+        <v>663</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>42</v>
@@ -10588,11 +11471,11 @@
       </c>
     </row>
     <row r="3" spans="1:34" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>63</v>
-      </c>
-      <c r="B3" t="s">
-        <v>419</v>
+      <c r="A3" t="s" s="0">
+        <v>177</v>
+      </c>
+      <c r="B3" t="s" s="0">
+        <v>664</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>42</v>
@@ -10656,11 +11539,11 @@
       </c>
     </row>
     <row r="4" spans="1:34" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>63</v>
-      </c>
-      <c r="B4" t="s">
-        <v>420</v>
+      <c r="A4" t="s" s="0">
+        <v>177</v>
+      </c>
+      <c r="B4" t="s" s="0">
+        <v>665</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>42</v>
@@ -10724,11 +11607,11 @@
       </c>
     </row>
     <row r="5" spans="1:34" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>63</v>
-      </c>
-      <c r="B5" t="s">
-        <v>421</v>
+      <c r="A5" t="s" s="0">
+        <v>177</v>
+      </c>
+      <c r="B5" t="s" s="0">
+        <v>666</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>42</v>
@@ -10792,11 +11675,11 @@
       </c>
     </row>
     <row r="6" spans="1:34" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
-        <v>63</v>
-      </c>
-      <c r="B6" t="s">
-        <v>422</v>
+      <c r="A6" t="s" s="0">
+        <v>177</v>
+      </c>
+      <c r="B6" t="s" s="0">
+        <v>667</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>42</v>
@@ -10860,11 +11743,11 @@
       </c>
     </row>
     <row r="7" spans="1:34" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
-        <v>63</v>
-      </c>
-      <c r="B7" t="s">
-        <v>423</v>
+      <c r="A7" t="s" s="0">
+        <v>177</v>
+      </c>
+      <c r="B7" t="s" s="0">
+        <v>668</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>42</v>
@@ -10928,11 +11811,11 @@
       </c>
     </row>
     <row r="8" spans="1:34" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
-        <v>63</v>
-      </c>
-      <c r="B8" t="s">
-        <v>424</v>
+      <c r="A8" t="s" s="0">
+        <v>177</v>
+      </c>
+      <c r="B8" t="s" s="0">
+        <v>669</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>42</v>
@@ -10996,11 +11879,11 @@
       </c>
     </row>
     <row r="9" spans="1:34" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
-        <v>63</v>
-      </c>
-      <c r="B9" t="s">
-        <v>425</v>
+      <c r="A9" t="s" s="0">
+        <v>177</v>
+      </c>
+      <c r="B9" t="s" s="0">
+        <v>670</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>42</v>
@@ -11064,11 +11947,11 @@
       </c>
     </row>
     <row r="10" spans="1:34" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
-        <v>63</v>
-      </c>
-      <c r="B10" t="s">
-        <v>426</v>
+      <c r="A10" t="s" s="0">
+        <v>177</v>
+      </c>
+      <c r="B10" t="s" s="0">
+        <v>671</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>42</v>
@@ -11267,9 +12150,9 @@
   <dimension ref="A1:AG52"/>
   <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="8.77734375" style="3" collapsed="1"/>
-    <col min="2" max="2" width="47.77734375" style="3" customWidth="1" collapsed="1"/>
-    <col min="3" max="16384" width="8.77734375" style="3" collapsed="1"/>
+    <col min="1" max="1" style="3" width="8.77734375" collapsed="true"/>
+    <col min="2" max="2" customWidth="true" style="3" width="47.77734375" collapsed="true"/>
+    <col min="3" max="16384" style="3" width="8.77734375" collapsed="true"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:33" ht="28.8" x14ac:dyDescent="0.3">
@@ -11374,11 +12257,11 @@
       </c>
     </row>
     <row r="2" spans="1:33" ht="72" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="3">
         <v>63</v>
       </c>
-      <c r="B2" t="s">
-        <v>183</v>
+      <c r="B2" t="s" s="3">
+        <v>428</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>28</v>
@@ -11441,11 +12324,11 @@
       </c>
     </row>
     <row r="3" spans="1:33" ht="72" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
+      <c r="A3" t="s" s="3">
         <v>63</v>
       </c>
-      <c r="B3" t="s">
-        <v>184</v>
+      <c r="B3" t="s" s="3">
+        <v>429</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>28</v>
@@ -11508,11 +12391,11 @@
       </c>
     </row>
     <row r="4" spans="1:33" ht="72" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
+      <c r="A4" t="s" s="3">
         <v>63</v>
       </c>
-      <c r="B4" t="s">
-        <v>185</v>
+      <c r="B4" t="s" s="3">
+        <v>430</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>28</v>
@@ -11575,11 +12458,11 @@
       </c>
     </row>
     <row r="5" spans="1:33" ht="72" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
+      <c r="A5" t="s" s="3">
         <v>63</v>
       </c>
-      <c r="B5" t="s">
-        <v>186</v>
+      <c r="B5" t="s" s="3">
+        <v>431</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>28</v>
@@ -11642,11 +12525,11 @@
       </c>
     </row>
     <row r="6" spans="1:33" ht="72" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
+      <c r="A6" t="s" s="3">
         <v>63</v>
       </c>
-      <c r="B6" t="s">
-        <v>187</v>
+      <c r="B6" t="s" s="3">
+        <v>432</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>28</v>
@@ -11709,11 +12592,11 @@
       </c>
     </row>
     <row r="7" spans="1:33" ht="72" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
+      <c r="A7" t="s" s="3">
         <v>63</v>
       </c>
-      <c r="B7" t="s">
-        <v>188</v>
+      <c r="B7" t="s" s="3">
+        <v>433</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>28</v>
@@ -11776,11 +12659,11 @@
       </c>
     </row>
     <row r="8" spans="1:33" ht="72" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
+      <c r="A8" t="s" s="3">
         <v>63</v>
       </c>
-      <c r="B8" t="s">
-        <v>189</v>
+      <c r="B8" t="s" s="3">
+        <v>434</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>28</v>
@@ -11843,11 +12726,11 @@
       </c>
     </row>
     <row r="9" spans="1:33" ht="72" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
+      <c r="A9" t="s" s="3">
         <v>63</v>
       </c>
-      <c r="B9" t="s">
-        <v>190</v>
+      <c r="B9" t="s" s="3">
+        <v>435</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>28</v>
@@ -11910,11 +12793,11 @@
       </c>
     </row>
     <row r="10" spans="1:33" ht="72" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
+      <c r="A10" t="s" s="3">
         <v>63</v>
       </c>
-      <c r="B10" t="s">
-        <v>191</v>
+      <c r="B10" t="s" s="3">
+        <v>436</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>28</v>
@@ -11977,11 +12860,11 @@
       </c>
     </row>
     <row r="11" spans="1:33" ht="72" x14ac:dyDescent="0.3">
-      <c r="A11" t="s">
+      <c r="A11" t="s" s="3">
         <v>63</v>
       </c>
-      <c r="B11" t="s">
-        <v>192</v>
+      <c r="B11" t="s" s="3">
+        <v>437</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>28</v>
@@ -12044,11 +12927,11 @@
       </c>
     </row>
     <row r="12" spans="1:33" ht="72" x14ac:dyDescent="0.3">
-      <c r="A12" t="s">
+      <c r="A12" t="s" s="3">
         <v>63</v>
       </c>
-      <c r="B12" t="s">
-        <v>193</v>
+      <c r="B12" t="s" s="3">
+        <v>438</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>28</v>
@@ -12111,11 +12994,11 @@
       </c>
     </row>
     <row r="13" spans="1:33" ht="72" x14ac:dyDescent="0.3">
-      <c r="A13" t="s">
+      <c r="A13" t="s" s="3">
         <v>63</v>
       </c>
-      <c r="B13" t="s">
-        <v>194</v>
+      <c r="B13" t="s" s="3">
+        <v>439</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>28</v>
@@ -12178,11 +13061,11 @@
       </c>
     </row>
     <row r="14" spans="1:33" ht="72" x14ac:dyDescent="0.3">
-      <c r="A14" t="s">
+      <c r="A14" t="s" s="3">
         <v>63</v>
       </c>
-      <c r="B14" t="s">
-        <v>195</v>
+      <c r="B14" t="s" s="3">
+        <v>440</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>28</v>
@@ -12245,11 +13128,11 @@
       </c>
     </row>
     <row r="15" spans="1:33" ht="72" x14ac:dyDescent="0.3">
-      <c r="A15" t="s">
+      <c r="A15" t="s" s="3">
         <v>63</v>
       </c>
-      <c r="B15" t="s">
-        <v>196</v>
+      <c r="B15" t="s" s="3">
+        <v>441</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>28</v>
@@ -12312,11 +13195,11 @@
       </c>
     </row>
     <row r="16" spans="1:33" ht="72" x14ac:dyDescent="0.3">
-      <c r="A16" t="s">
+      <c r="A16" t="s" s="3">
         <v>63</v>
       </c>
-      <c r="B16" t="s">
-        <v>197</v>
+      <c r="B16" t="s" s="3">
+        <v>442</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>28</v>
@@ -12379,11 +13262,11 @@
       </c>
     </row>
     <row r="17" spans="1:33" ht="72" x14ac:dyDescent="0.3">
-      <c r="A17" t="s">
+      <c r="A17" t="s" s="3">
         <v>63</v>
       </c>
-      <c r="B17" t="s">
-        <v>198</v>
+      <c r="B17" t="s" s="3">
+        <v>443</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>28</v>
@@ -12446,11 +13329,11 @@
       </c>
     </row>
     <row r="18" spans="1:33" ht="72" x14ac:dyDescent="0.3">
-      <c r="A18" t="s">
+      <c r="A18" t="s" s="3">
         <v>63</v>
       </c>
-      <c r="B18" t="s">
-        <v>199</v>
+      <c r="B18" t="s" s="3">
+        <v>444</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>28</v>
@@ -12513,11 +13396,11 @@
       </c>
     </row>
     <row r="19" spans="1:33" ht="72" x14ac:dyDescent="0.3">
-      <c r="A19" t="s">
+      <c r="A19" t="s" s="3">
         <v>63</v>
       </c>
-      <c r="B19" t="s">
-        <v>200</v>
+      <c r="B19" t="s" s="3">
+        <v>445</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>28</v>
@@ -12580,11 +13463,11 @@
       </c>
     </row>
     <row r="20" spans="1:33" ht="72" x14ac:dyDescent="0.3">
-      <c r="A20" t="s">
+      <c r="A20" t="s" s="3">
         <v>63</v>
       </c>
-      <c r="B20" t="s">
-        <v>201</v>
+      <c r="B20" t="s" s="3">
+        <v>446</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>28</v>
@@ -12647,11 +13530,11 @@
       </c>
     </row>
     <row r="21" spans="1:33" ht="72" x14ac:dyDescent="0.3">
-      <c r="A21" t="s">
+      <c r="A21" t="s" s="3">
         <v>63</v>
       </c>
-      <c r="B21" t="s">
-        <v>202</v>
+      <c r="B21" t="s" s="3">
+        <v>447</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>28</v>
@@ -12714,11 +13597,11 @@
       </c>
     </row>
     <row r="22" spans="1:33" ht="72" x14ac:dyDescent="0.3">
-      <c r="A22" t="s">
+      <c r="A22" t="s" s="3">
         <v>63</v>
       </c>
-      <c r="B22" t="s">
-        <v>203</v>
+      <c r="B22" t="s" s="3">
+        <v>448</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>28</v>
@@ -12781,11 +13664,11 @@
       </c>
     </row>
     <row r="23" spans="1:33" ht="72" x14ac:dyDescent="0.3">
-      <c r="A23" t="s">
+      <c r="A23" t="s" s="3">
         <v>63</v>
       </c>
-      <c r="B23" t="s">
-        <v>204</v>
+      <c r="B23" t="s" s="3">
+        <v>449</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>28</v>
@@ -12848,11 +13731,11 @@
       </c>
     </row>
     <row r="24" spans="1:33" ht="72" x14ac:dyDescent="0.3">
-      <c r="A24" t="s">
+      <c r="A24" t="s" s="3">
         <v>63</v>
       </c>
-      <c r="B24" t="s">
-        <v>205</v>
+      <c r="B24" t="s" s="3">
+        <v>450</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>28</v>
@@ -12915,11 +13798,11 @@
       </c>
     </row>
     <row r="25" spans="1:33" ht="72" x14ac:dyDescent="0.3">
-      <c r="A25" t="s">
+      <c r="A25" t="s" s="3">
         <v>63</v>
       </c>
-      <c r="B25" t="s">
-        <v>206</v>
+      <c r="B25" t="s" s="3">
+        <v>451</v>
       </c>
       <c r="C25" s="1" t="s">
         <v>28</v>
@@ -12982,11 +13865,11 @@
       </c>
     </row>
     <row r="26" spans="1:33" ht="72" x14ac:dyDescent="0.3">
-      <c r="A26" t="s">
+      <c r="A26" t="s" s="3">
         <v>63</v>
       </c>
-      <c r="B26" t="s">
-        <v>207</v>
+      <c r="B26" t="s" s="3">
+        <v>452</v>
       </c>
       <c r="C26" s="1" t="s">
         <v>28</v>
@@ -13049,11 +13932,11 @@
       </c>
     </row>
     <row r="27" spans="1:33" ht="72" x14ac:dyDescent="0.3">
-      <c r="A27" t="s">
+      <c r="A27" t="s" s="3">
         <v>63</v>
       </c>
-      <c r="B27" t="s">
-        <v>208</v>
+      <c r="B27" t="s" s="3">
+        <v>453</v>
       </c>
       <c r="C27" s="1" t="s">
         <v>28</v>
@@ -13116,11 +13999,11 @@
       </c>
     </row>
     <row r="28" spans="1:33" ht="72" x14ac:dyDescent="0.3">
-      <c r="A28" t="s">
+      <c r="A28" t="s" s="3">
         <v>63</v>
       </c>
-      <c r="B28" t="s">
-        <v>209</v>
+      <c r="B28" t="s" s="3">
+        <v>454</v>
       </c>
       <c r="C28" s="1" t="s">
         <v>28</v>
@@ -13183,11 +14066,11 @@
       </c>
     </row>
     <row r="29" spans="1:33" ht="72" x14ac:dyDescent="0.3">
-      <c r="A29" t="s">
+      <c r="A29" t="s" s="3">
         <v>63</v>
       </c>
-      <c r="B29" t="s">
-        <v>210</v>
+      <c r="B29" t="s" s="3">
+        <v>455</v>
       </c>
       <c r="C29" s="1" t="s">
         <v>28</v>
@@ -13250,11 +14133,11 @@
       </c>
     </row>
     <row r="30" spans="1:33" ht="72" x14ac:dyDescent="0.3">
-      <c r="A30" t="s">
+      <c r="A30" t="s" s="3">
         <v>63</v>
       </c>
-      <c r="B30" t="s">
-        <v>211</v>
+      <c r="B30" t="s" s="3">
+        <v>456</v>
       </c>
       <c r="C30" s="1" t="s">
         <v>28</v>
@@ -13317,11 +14200,11 @@
       </c>
     </row>
     <row r="31" spans="1:33" ht="72" x14ac:dyDescent="0.3">
-      <c r="A31" t="s">
+      <c r="A31" t="s" s="3">
         <v>63</v>
       </c>
-      <c r="B31" t="s">
-        <v>212</v>
+      <c r="B31" t="s" s="3">
+        <v>457</v>
       </c>
       <c r="C31" s="1" t="s">
         <v>28</v>
@@ -13384,11 +14267,11 @@
       </c>
     </row>
     <row r="32" spans="1:33" ht="72" x14ac:dyDescent="0.3">
-      <c r="A32" t="s">
+      <c r="A32" t="s" s="3">
         <v>63</v>
       </c>
-      <c r="B32" t="s">
-        <v>213</v>
+      <c r="B32" t="s" s="3">
+        <v>458</v>
       </c>
       <c r="C32" s="1" t="s">
         <v>28</v>
@@ -13451,11 +14334,11 @@
       </c>
     </row>
     <row r="33" spans="1:33" ht="72" x14ac:dyDescent="0.3">
-      <c r="A33" t="s">
+      <c r="A33" t="s" s="3">
         <v>63</v>
       </c>
-      <c r="B33" t="s">
-        <v>214</v>
+      <c r="B33" t="s" s="3">
+        <v>459</v>
       </c>
       <c r="C33" s="1" t="s">
         <v>28</v>
@@ -13518,11 +14401,11 @@
       </c>
     </row>
     <row r="34" spans="1:33" ht="72" x14ac:dyDescent="0.3">
-      <c r="A34" t="s">
-        <v>177</v>
-      </c>
-      <c r="B34" t="s">
-        <v>215</v>
+      <c r="A34" t="s" s="3">
+        <v>63</v>
+      </c>
+      <c r="B34" t="s" s="3">
+        <v>460</v>
       </c>
       <c r="C34" s="1" t="s">
         <v>28</v>
@@ -13585,11 +14468,11 @@
       </c>
     </row>
     <row r="35" spans="1:33" ht="72" x14ac:dyDescent="0.3">
-      <c r="A35" t="s">
-        <v>177</v>
-      </c>
-      <c r="B35" t="s">
-        <v>216</v>
+      <c r="A35" t="s" s="3">
+        <v>63</v>
+      </c>
+      <c r="B35" t="s" s="3">
+        <v>461</v>
       </c>
       <c r="C35" s="1" t="s">
         <v>28</v>
@@ -13652,11 +14535,11 @@
       </c>
     </row>
     <row r="36" spans="1:33" ht="72" x14ac:dyDescent="0.3">
-      <c r="A36" t="s">
-        <v>177</v>
-      </c>
-      <c r="B36" t="s">
-        <v>217</v>
+      <c r="A36" t="s" s="3">
+        <v>63</v>
+      </c>
+      <c r="B36" t="s" s="3">
+        <v>462</v>
       </c>
       <c r="C36" s="1" t="s">
         <v>28</v>
@@ -13719,11 +14602,11 @@
       </c>
     </row>
     <row r="37" spans="1:33" ht="72" x14ac:dyDescent="0.3">
-      <c r="A37" t="s">
-        <v>177</v>
-      </c>
-      <c r="B37" t="s">
-        <v>218</v>
+      <c r="A37" t="s" s="3">
+        <v>63</v>
+      </c>
+      <c r="B37" t="s" s="3">
+        <v>463</v>
       </c>
       <c r="C37" s="1" t="s">
         <v>28</v>
@@ -13786,11 +14669,11 @@
       </c>
     </row>
     <row r="38" spans="1:33" ht="72" x14ac:dyDescent="0.3">
-      <c r="A38" t="s">
-        <v>177</v>
-      </c>
-      <c r="B38" t="s">
-        <v>219</v>
+      <c r="A38" t="s" s="3">
+        <v>63</v>
+      </c>
+      <c r="B38" t="s" s="3">
+        <v>464</v>
       </c>
       <c r="C38" s="1" t="s">
         <v>28</v>
@@ -13853,11 +14736,11 @@
       </c>
     </row>
     <row r="39" spans="1:33" ht="72" x14ac:dyDescent="0.3">
-      <c r="A39" t="s">
-        <v>177</v>
-      </c>
-      <c r="B39" t="s">
-        <v>220</v>
+      <c r="A39" t="s" s="3">
+        <v>63</v>
+      </c>
+      <c r="B39" t="s" s="3">
+        <v>465</v>
       </c>
       <c r="C39" s="1" t="s">
         <v>28</v>
@@ -13920,11 +14803,11 @@
       </c>
     </row>
     <row r="40" spans="1:33" ht="72" x14ac:dyDescent="0.3">
-      <c r="A40" t="s">
-        <v>177</v>
-      </c>
-      <c r="B40" t="s">
-        <v>221</v>
+      <c r="A40" t="s" s="3">
+        <v>63</v>
+      </c>
+      <c r="B40" t="s" s="3">
+        <v>466</v>
       </c>
       <c r="C40" s="1" t="s">
         <v>28</v>
@@ -13987,11 +14870,11 @@
       </c>
     </row>
     <row r="41" spans="1:33" ht="72" x14ac:dyDescent="0.3">
-      <c r="A41" t="s">
-        <v>177</v>
-      </c>
-      <c r="B41" t="s">
-        <v>222</v>
+      <c r="A41" t="s" s="3">
+        <v>63</v>
+      </c>
+      <c r="B41" t="s" s="3">
+        <v>467</v>
       </c>
       <c r="C41" s="1" t="s">
         <v>28</v>
@@ -14054,11 +14937,11 @@
       </c>
     </row>
     <row r="42" spans="1:33" ht="72" x14ac:dyDescent="0.3">
-      <c r="A42" t="s">
+      <c r="A42" t="s" s="3">
         <v>63</v>
       </c>
-      <c r="B42" t="s">
-        <v>223</v>
+      <c r="B42" t="s" s="3">
+        <v>468</v>
       </c>
       <c r="C42" s="1" t="s">
         <v>28</v>
@@ -14121,11 +15004,11 @@
       </c>
     </row>
     <row r="43" spans="1:33" ht="72" x14ac:dyDescent="0.3">
-      <c r="A43" t="s">
+      <c r="A43" t="s" s="3">
         <v>63</v>
       </c>
-      <c r="B43" t="s">
-        <v>224</v>
+      <c r="B43" t="s" s="3">
+        <v>469</v>
       </c>
       <c r="C43" s="1" t="s">
         <v>28</v>
@@ -14188,11 +15071,11 @@
       </c>
     </row>
     <row r="44" spans="1:33" ht="72" x14ac:dyDescent="0.3">
-      <c r="A44" t="s">
+      <c r="A44" t="s" s="3">
         <v>63</v>
       </c>
-      <c r="B44" t="s">
-        <v>225</v>
+      <c r="B44" t="s" s="3">
+        <v>470</v>
       </c>
       <c r="C44" s="1" t="s">
         <v>28</v>
@@ -14255,11 +15138,11 @@
       </c>
     </row>
     <row r="45" spans="1:33" ht="72" x14ac:dyDescent="0.3">
-      <c r="A45" t="s">
+      <c r="A45" t="s" s="3">
         <v>63</v>
       </c>
-      <c r="B45" t="s">
-        <v>226</v>
+      <c r="B45" t="s" s="3">
+        <v>471</v>
       </c>
       <c r="C45" s="1" t="s">
         <v>28</v>
@@ -14322,11 +15205,11 @@
       </c>
     </row>
     <row r="46" spans="1:33" ht="72" x14ac:dyDescent="0.3">
-      <c r="A46" t="s">
+      <c r="A46" t="s" s="3">
         <v>63</v>
       </c>
-      <c r="B46" t="s">
-        <v>227</v>
+      <c r="B46" t="s" s="3">
+        <v>472</v>
       </c>
       <c r="C46" s="1" t="s">
         <v>28</v>
@@ -14389,11 +15272,11 @@
       </c>
     </row>
     <row r="47" spans="1:33" ht="72" x14ac:dyDescent="0.3">
-      <c r="A47" t="s">
+      <c r="A47" t="s" s="3">
         <v>63</v>
       </c>
-      <c r="B47" t="s">
-        <v>228</v>
+      <c r="B47" t="s" s="3">
+        <v>473</v>
       </c>
       <c r="C47" s="1" t="s">
         <v>28</v>
@@ -14456,11 +15339,11 @@
       </c>
     </row>
     <row r="48" spans="1:33" ht="72" x14ac:dyDescent="0.3">
-      <c r="A48" t="s">
+      <c r="A48" t="s" s="3">
         <v>63</v>
       </c>
-      <c r="B48" t="s">
-        <v>229</v>
+      <c r="B48" t="s" s="3">
+        <v>474</v>
       </c>
       <c r="C48" s="1" t="s">
         <v>28</v>
@@ -14523,11 +15406,11 @@
       </c>
     </row>
     <row r="49" spans="1:33" ht="72" x14ac:dyDescent="0.3">
-      <c r="A49" t="s">
+      <c r="A49" t="s" s="3">
         <v>63</v>
       </c>
-      <c r="B49" t="s">
-        <v>230</v>
+      <c r="B49" t="s" s="3">
+        <v>475</v>
       </c>
       <c r="C49" s="1" t="s">
         <v>28</v>
@@ -14590,11 +15473,11 @@
       </c>
     </row>
     <row r="50" spans="1:33" ht="72" x14ac:dyDescent="0.3">
-      <c r="A50" t="s">
+      <c r="A50" t="s" s="3">
         <v>63</v>
       </c>
-      <c r="B50" t="s">
-        <v>231</v>
+      <c r="B50" t="s" s="3">
+        <v>476</v>
       </c>
       <c r="C50" s="1" t="s">
         <v>28</v>
@@ -14673,9 +15556,9 @@
   <dimension ref="A1:AG50"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="22.21875" customWidth="1" collapsed="1"/>
-    <col min="20" max="20" width="20.77734375" customWidth="1" collapsed="1"/>
-    <col min="29" max="29" width="8.77734375" style="3" collapsed="1"/>
+    <col min="2" max="2" customWidth="true" width="22.21875" collapsed="true"/>
+    <col min="20" max="20" customWidth="true" width="20.77734375" collapsed="true"/>
+    <col min="29" max="29" style="3" width="8.77734375" collapsed="true"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:33" ht="28.8" x14ac:dyDescent="0.3">
@@ -14780,11 +15663,11 @@
       </c>
     </row>
     <row r="2" spans="1:33" ht="72" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>63</v>
       </c>
-      <c r="B2" t="s">
-        <v>232</v>
+      <c r="B2" t="s" s="0">
+        <v>477</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>28</v>
@@ -14847,11 +15730,11 @@
       </c>
     </row>
     <row r="3" spans="1:33" ht="72" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
+      <c r="A3" t="s" s="0">
         <v>63</v>
       </c>
-      <c r="B3" t="s">
-        <v>233</v>
+      <c r="B3" t="s" s="0">
+        <v>478</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>28</v>
@@ -14914,11 +15797,11 @@
       </c>
     </row>
     <row r="4" spans="1:33" ht="72" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
+      <c r="A4" t="s" s="0">
         <v>63</v>
       </c>
-      <c r="B4" t="s">
-        <v>234</v>
+      <c r="B4" t="s" s="0">
+        <v>479</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>28</v>
@@ -14981,11 +15864,11 @@
       </c>
     </row>
     <row r="5" spans="1:33" ht="72" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
+      <c r="A5" t="s" s="0">
         <v>63</v>
       </c>
-      <c r="B5" t="s">
-        <v>235</v>
+      <c r="B5" t="s" s="0">
+        <v>480</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>28</v>
@@ -15048,11 +15931,11 @@
       </c>
     </row>
     <row r="6" spans="1:33" ht="72" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
+      <c r="A6" t="s" s="0">
         <v>63</v>
       </c>
-      <c r="B6" t="s">
-        <v>236</v>
+      <c r="B6" t="s" s="0">
+        <v>481</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>28</v>
@@ -15115,11 +15998,11 @@
       </c>
     </row>
     <row r="7" spans="1:33" ht="72" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
+      <c r="A7" t="s" s="0">
         <v>63</v>
       </c>
-      <c r="B7" t="s">
-        <v>237</v>
+      <c r="B7" t="s" s="0">
+        <v>482</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>28</v>
@@ -15182,11 +16065,11 @@
       </c>
     </row>
     <row r="8" spans="1:33" ht="72" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
+      <c r="A8" t="s" s="0">
         <v>63</v>
       </c>
-      <c r="B8" t="s">
-        <v>238</v>
+      <c r="B8" t="s" s="0">
+        <v>483</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>28</v>
@@ -15249,11 +16132,11 @@
       </c>
     </row>
     <row r="9" spans="1:33" ht="72" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
+      <c r="A9" t="s" s="0">
         <v>63</v>
       </c>
-      <c r="B9" t="s">
-        <v>239</v>
+      <c r="B9" t="s" s="0">
+        <v>484</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>28</v>
@@ -15316,11 +16199,11 @@
       </c>
     </row>
     <row r="10" spans="1:33" ht="72" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
+      <c r="A10" t="s" s="0">
         <v>63</v>
       </c>
-      <c r="B10" t="s">
-        <v>240</v>
+      <c r="B10" t="s" s="0">
+        <v>485</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>28</v>
@@ -15383,11 +16266,11 @@
       </c>
     </row>
     <row r="11" spans="1:33" ht="72" x14ac:dyDescent="0.3">
-      <c r="A11" t="s">
+      <c r="A11" t="s" s="0">
         <v>63</v>
       </c>
-      <c r="B11" t="s">
-        <v>241</v>
+      <c r="B11" t="s" s="0">
+        <v>486</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>28</v>
@@ -15450,11 +16333,11 @@
       </c>
     </row>
     <row r="12" spans="1:33" ht="72" x14ac:dyDescent="0.3">
-      <c r="A12" t="s">
+      <c r="A12" t="s" s="0">
         <v>63</v>
       </c>
-      <c r="B12" t="s">
-        <v>242</v>
+      <c r="B12" t="s" s="0">
+        <v>487</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>28</v>
@@ -15517,11 +16400,11 @@
       </c>
     </row>
     <row r="13" spans="1:33" ht="72" x14ac:dyDescent="0.3">
-      <c r="A13" t="s">
+      <c r="A13" t="s" s="0">
         <v>63</v>
       </c>
-      <c r="B13" t="s">
-        <v>243</v>
+      <c r="B13" t="s" s="0">
+        <v>488</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>28</v>
@@ -15584,11 +16467,11 @@
       </c>
     </row>
     <row r="14" spans="1:33" ht="72" x14ac:dyDescent="0.3">
-      <c r="A14" t="s">
+      <c r="A14" t="s" s="0">
         <v>63</v>
       </c>
-      <c r="B14" t="s">
-        <v>244</v>
+      <c r="B14" t="s" s="0">
+        <v>489</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>28</v>
@@ -15651,11 +16534,11 @@
       </c>
     </row>
     <row r="15" spans="1:33" ht="72" x14ac:dyDescent="0.3">
-      <c r="A15" t="s">
+      <c r="A15" t="s" s="0">
         <v>63</v>
       </c>
-      <c r="B15" t="s">
-        <v>245</v>
+      <c r="B15" t="s" s="0">
+        <v>490</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>28</v>
@@ -15718,11 +16601,11 @@
       </c>
     </row>
     <row r="16" spans="1:33" ht="72" x14ac:dyDescent="0.3">
-      <c r="A16" t="s">
+      <c r="A16" t="s" s="0">
         <v>63</v>
       </c>
-      <c r="B16" t="s">
-        <v>246</v>
+      <c r="B16" t="s" s="0">
+        <v>491</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>28</v>
@@ -15785,11 +16668,11 @@
       </c>
     </row>
     <row r="17" spans="1:33" ht="72" x14ac:dyDescent="0.3">
-      <c r="A17" t="s">
+      <c r="A17" t="s" s="0">
         <v>63</v>
       </c>
-      <c r="B17" t="s">
-        <v>247</v>
+      <c r="B17" t="s" s="0">
+        <v>492</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>28</v>
@@ -15852,11 +16735,11 @@
       </c>
     </row>
     <row r="18" spans="1:33" ht="72" x14ac:dyDescent="0.3">
-      <c r="A18" t="s">
+      <c r="A18" t="s" s="0">
         <v>63</v>
       </c>
-      <c r="B18" t="s">
-        <v>248</v>
+      <c r="B18" t="s" s="0">
+        <v>493</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>28</v>
@@ -15919,11 +16802,11 @@
       </c>
     </row>
     <row r="19" spans="1:33" ht="72" x14ac:dyDescent="0.3">
-      <c r="A19" t="s">
+      <c r="A19" t="s" s="0">
         <v>63</v>
       </c>
-      <c r="B19" t="s">
-        <v>249</v>
+      <c r="B19" t="s" s="0">
+        <v>494</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>28</v>
@@ -15986,11 +16869,11 @@
       </c>
     </row>
     <row r="20" spans="1:33" ht="72" x14ac:dyDescent="0.3">
-      <c r="A20" t="s">
+      <c r="A20" t="s" s="0">
         <v>63</v>
       </c>
-      <c r="B20" t="s">
-        <v>250</v>
+      <c r="B20" t="s" s="0">
+        <v>495</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>28</v>
@@ -16053,11 +16936,11 @@
       </c>
     </row>
     <row r="21" spans="1:33" ht="72" x14ac:dyDescent="0.3">
-      <c r="A21" t="s">
+      <c r="A21" t="s" s="0">
         <v>63</v>
       </c>
-      <c r="B21" t="s">
-        <v>251</v>
+      <c r="B21" t="s" s="0">
+        <v>496</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>28</v>
@@ -16120,11 +17003,11 @@
       </c>
     </row>
     <row r="22" spans="1:33" ht="72" x14ac:dyDescent="0.3">
-      <c r="A22" t="s">
+      <c r="A22" t="s" s="0">
         <v>63</v>
       </c>
-      <c r="B22" t="s">
-        <v>252</v>
+      <c r="B22" t="s" s="0">
+        <v>497</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>28</v>
@@ -16187,11 +17070,11 @@
       </c>
     </row>
     <row r="23" spans="1:33" ht="72" x14ac:dyDescent="0.3">
-      <c r="A23" t="s">
+      <c r="A23" t="s" s="0">
         <v>63</v>
       </c>
-      <c r="B23" t="s">
-        <v>253</v>
+      <c r="B23" t="s" s="0">
+        <v>498</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>28</v>
@@ -16254,11 +17137,11 @@
       </c>
     </row>
     <row r="24" spans="1:33" ht="72" x14ac:dyDescent="0.3">
-      <c r="A24" t="s">
+      <c r="A24" t="s" s="0">
         <v>63</v>
       </c>
-      <c r="B24" t="s">
-        <v>254</v>
+      <c r="B24" t="s" s="0">
+        <v>499</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>28</v>
@@ -16321,11 +17204,11 @@
       </c>
     </row>
     <row r="25" spans="1:33" ht="72" x14ac:dyDescent="0.3">
-      <c r="A25" t="s">
+      <c r="A25" t="s" s="0">
         <v>63</v>
       </c>
-      <c r="B25" t="s">
-        <v>255</v>
+      <c r="B25" t="s" s="0">
+        <v>500</v>
       </c>
       <c r="C25" s="1" t="s">
         <v>28</v>
@@ -16388,11 +17271,11 @@
       </c>
     </row>
     <row r="26" spans="1:33" ht="72" x14ac:dyDescent="0.3">
-      <c r="A26" t="s">
+      <c r="A26" t="s" s="0">
         <v>63</v>
       </c>
-      <c r="B26" t="s">
-        <v>256</v>
+      <c r="B26" t="s" s="0">
+        <v>501</v>
       </c>
       <c r="C26" s="1" t="s">
         <v>28</v>
@@ -16455,11 +17338,11 @@
       </c>
     </row>
     <row r="27" spans="1:33" ht="72" x14ac:dyDescent="0.3">
-      <c r="A27" t="s">
+      <c r="A27" t="s" s="0">
         <v>63</v>
       </c>
-      <c r="B27" t="s">
-        <v>257</v>
+      <c r="B27" t="s" s="0">
+        <v>502</v>
       </c>
       <c r="C27" s="1" t="s">
         <v>28</v>
@@ -16522,11 +17405,11 @@
       </c>
     </row>
     <row r="28" spans="1:33" ht="72" x14ac:dyDescent="0.3">
-      <c r="A28" t="s">
+      <c r="A28" t="s" s="0">
         <v>63</v>
       </c>
-      <c r="B28" t="s">
-        <v>258</v>
+      <c r="B28" t="s" s="0">
+        <v>503</v>
       </c>
       <c r="C28" s="1" t="s">
         <v>28</v>
@@ -16589,11 +17472,11 @@
       </c>
     </row>
     <row r="29" spans="1:33" ht="72" x14ac:dyDescent="0.3">
-      <c r="A29" t="s">
+      <c r="A29" t="s" s="0">
         <v>63</v>
       </c>
-      <c r="B29" t="s">
-        <v>259</v>
+      <c r="B29" t="s" s="0">
+        <v>504</v>
       </c>
       <c r="C29" s="1" t="s">
         <v>28</v>
@@ -16656,11 +17539,11 @@
       </c>
     </row>
     <row r="30" spans="1:33" ht="72" x14ac:dyDescent="0.3">
-      <c r="A30" t="s">
+      <c r="A30" t="s" s="0">
         <v>63</v>
       </c>
-      <c r="B30" t="s">
-        <v>260</v>
+      <c r="B30" t="s" s="0">
+        <v>505</v>
       </c>
       <c r="C30" s="1" t="s">
         <v>28</v>
@@ -16723,11 +17606,11 @@
       </c>
     </row>
     <row r="31" spans="1:33" ht="72" x14ac:dyDescent="0.3">
-      <c r="A31" t="s">
+      <c r="A31" t="s" s="0">
         <v>63</v>
       </c>
-      <c r="B31" t="s">
-        <v>261</v>
+      <c r="B31" t="s" s="0">
+        <v>506</v>
       </c>
       <c r="C31" s="1" t="s">
         <v>28</v>
@@ -16790,11 +17673,11 @@
       </c>
     </row>
     <row r="32" spans="1:33" ht="72" x14ac:dyDescent="0.3">
-      <c r="A32" t="s">
+      <c r="A32" t="s" s="0">
         <v>63</v>
       </c>
-      <c r="B32" t="s">
-        <v>262</v>
+      <c r="B32" t="s" s="0">
+        <v>507</v>
       </c>
       <c r="C32" s="1" t="s">
         <v>28</v>
@@ -16857,11 +17740,11 @@
       </c>
     </row>
     <row r="33" spans="1:33" ht="72" x14ac:dyDescent="0.3">
-      <c r="A33" t="s">
+      <c r="A33" t="s" s="0">
         <v>63</v>
       </c>
-      <c r="B33" t="s">
-        <v>263</v>
+      <c r="B33" t="s" s="0">
+        <v>508</v>
       </c>
       <c r="C33" s="1" t="s">
         <v>28</v>
@@ -16924,11 +17807,11 @@
       </c>
     </row>
     <row r="34" spans="1:33" ht="72" x14ac:dyDescent="0.3">
-      <c r="A34" t="s">
-        <v>177</v>
-      </c>
-      <c r="B34" t="s">
-        <v>264</v>
+      <c r="A34" t="s" s="0">
+        <v>63</v>
+      </c>
+      <c r="B34" t="s" s="0">
+        <v>509</v>
       </c>
       <c r="C34" s="1" t="s">
         <v>28</v>
@@ -16991,11 +17874,11 @@
       </c>
     </row>
     <row r="35" spans="1:33" ht="72" x14ac:dyDescent="0.3">
-      <c r="A35" t="s">
-        <v>177</v>
-      </c>
-      <c r="B35" t="s">
-        <v>265</v>
+      <c r="A35" t="s" s="0">
+        <v>63</v>
+      </c>
+      <c r="B35" t="s" s="0">
+        <v>510</v>
       </c>
       <c r="C35" s="1" t="s">
         <v>28</v>
@@ -17058,11 +17941,11 @@
       </c>
     </row>
     <row r="36" spans="1:33" ht="72" x14ac:dyDescent="0.3">
-      <c r="A36" t="s">
-        <v>177</v>
-      </c>
-      <c r="B36" t="s">
-        <v>266</v>
+      <c r="A36" t="s" s="0">
+        <v>63</v>
+      </c>
+      <c r="B36" t="s" s="0">
+        <v>511</v>
       </c>
       <c r="C36" s="1" t="s">
         <v>28</v>
@@ -17125,11 +18008,11 @@
       </c>
     </row>
     <row r="37" spans="1:33" ht="72" x14ac:dyDescent="0.3">
-      <c r="A37" t="s">
-        <v>177</v>
-      </c>
-      <c r="B37" t="s">
-        <v>267</v>
+      <c r="A37" t="s" s="0">
+        <v>63</v>
+      </c>
+      <c r="B37" t="s" s="0">
+        <v>512</v>
       </c>
       <c r="C37" s="1" t="s">
         <v>28</v>
@@ -17192,11 +18075,11 @@
       </c>
     </row>
     <row r="38" spans="1:33" ht="72" x14ac:dyDescent="0.3">
-      <c r="A38" t="s">
-        <v>177</v>
-      </c>
-      <c r="B38" t="s">
-        <v>268</v>
+      <c r="A38" t="s" s="0">
+        <v>63</v>
+      </c>
+      <c r="B38" t="s" s="0">
+        <v>513</v>
       </c>
       <c r="C38" s="1" t="s">
         <v>28</v>
@@ -17259,11 +18142,11 @@
       </c>
     </row>
     <row r="39" spans="1:33" ht="72" x14ac:dyDescent="0.3">
-      <c r="A39" t="s">
-        <v>177</v>
-      </c>
-      <c r="B39" t="s">
-        <v>269</v>
+      <c r="A39" t="s" s="0">
+        <v>63</v>
+      </c>
+      <c r="B39" t="s" s="0">
+        <v>514</v>
       </c>
       <c r="C39" s="1" t="s">
         <v>28</v>
@@ -17326,11 +18209,11 @@
       </c>
     </row>
     <row r="40" spans="1:33" ht="72" x14ac:dyDescent="0.3">
-      <c r="A40" t="s">
-        <v>177</v>
-      </c>
-      <c r="B40" t="s">
-        <v>270</v>
+      <c r="A40" t="s" s="0">
+        <v>63</v>
+      </c>
+      <c r="B40" t="s" s="0">
+        <v>515</v>
       </c>
       <c r="C40" s="1" t="s">
         <v>28</v>
@@ -17393,11 +18276,11 @@
       </c>
     </row>
     <row r="41" spans="1:33" ht="72" x14ac:dyDescent="0.3">
-      <c r="A41" t="s">
-        <v>177</v>
-      </c>
-      <c r="B41" t="s">
-        <v>271</v>
+      <c r="A41" t="s" s="0">
+        <v>63</v>
+      </c>
+      <c r="B41" t="s" s="0">
+        <v>516</v>
       </c>
       <c r="C41" s="1" t="s">
         <v>28</v>
@@ -17460,11 +18343,11 @@
       </c>
     </row>
     <row r="42" spans="1:33" ht="72" x14ac:dyDescent="0.3">
-      <c r="A42" t="s">
+      <c r="A42" t="s" s="0">
         <v>63</v>
       </c>
-      <c r="B42" t="s">
-        <v>272</v>
+      <c r="B42" t="s" s="0">
+        <v>517</v>
       </c>
       <c r="C42" s="1" t="s">
         <v>28</v>
@@ -17527,11 +18410,11 @@
       </c>
     </row>
     <row r="43" spans="1:33" ht="72" x14ac:dyDescent="0.3">
-      <c r="A43" t="s">
+      <c r="A43" t="s" s="0">
         <v>63</v>
       </c>
-      <c r="B43" t="s">
-        <v>273</v>
+      <c r="B43" t="s" s="0">
+        <v>518</v>
       </c>
       <c r="C43" s="1" t="s">
         <v>28</v>
@@ -17594,11 +18477,11 @@
       </c>
     </row>
     <row r="44" spans="1:33" ht="72" x14ac:dyDescent="0.3">
-      <c r="A44" t="s">
+      <c r="A44" t="s" s="0">
         <v>63</v>
       </c>
-      <c r="B44" t="s">
-        <v>274</v>
+      <c r="B44" t="s" s="0">
+        <v>519</v>
       </c>
       <c r="C44" s="1" t="s">
         <v>28</v>
@@ -17661,11 +18544,11 @@
       </c>
     </row>
     <row r="45" spans="1:33" ht="72" x14ac:dyDescent="0.3">
-      <c r="A45" t="s">
+      <c r="A45" t="s" s="0">
         <v>63</v>
       </c>
-      <c r="B45" t="s">
-        <v>275</v>
+      <c r="B45" t="s" s="0">
+        <v>520</v>
       </c>
       <c r="C45" s="1" t="s">
         <v>28</v>
@@ -17728,11 +18611,11 @@
       </c>
     </row>
     <row r="46" spans="1:33" ht="72" x14ac:dyDescent="0.3">
-      <c r="A46" t="s">
+      <c r="A46" t="s" s="0">
         <v>63</v>
       </c>
-      <c r="B46" t="s">
-        <v>276</v>
+      <c r="B46" t="s" s="0">
+        <v>521</v>
       </c>
       <c r="C46" s="1" t="s">
         <v>28</v>
@@ -17795,11 +18678,11 @@
       </c>
     </row>
     <row r="47" spans="1:33" ht="72" x14ac:dyDescent="0.3">
-      <c r="A47" t="s">
+      <c r="A47" t="s" s="0">
         <v>63</v>
       </c>
-      <c r="B47" t="s">
-        <v>277</v>
+      <c r="B47" t="s" s="0">
+        <v>522</v>
       </c>
       <c r="C47" s="1" t="s">
         <v>28</v>
@@ -17862,11 +18745,11 @@
       </c>
     </row>
     <row r="48" spans="1:33" ht="72" x14ac:dyDescent="0.3">
-      <c r="A48" t="s">
+      <c r="A48" t="s" s="0">
         <v>63</v>
       </c>
-      <c r="B48" t="s">
-        <v>278</v>
+      <c r="B48" t="s" s="0">
+        <v>523</v>
       </c>
       <c r="C48" s="1" t="s">
         <v>28</v>
@@ -17929,11 +18812,11 @@
       </c>
     </row>
     <row r="49" spans="1:33" ht="72" x14ac:dyDescent="0.3">
-      <c r="A49" t="s">
+      <c r="A49" t="s" s="0">
         <v>63</v>
       </c>
-      <c r="B49" t="s">
-        <v>279</v>
+      <c r="B49" t="s" s="0">
+        <v>524</v>
       </c>
       <c r="C49" s="1" t="s">
         <v>28</v>
@@ -17996,11 +18879,11 @@
       </c>
     </row>
     <row r="50" spans="1:33" ht="72" x14ac:dyDescent="0.3">
-      <c r="A50" t="s">
+      <c r="A50" t="s" s="0">
         <v>63</v>
       </c>
-      <c r="B50" t="s">
-        <v>280</v>
+      <c r="B50" t="s" s="0">
+        <v>525</v>
       </c>
       <c r="C50" s="1" t="s">
         <v>28</v>
@@ -18073,8 +18956,8 @@
   <dimension ref="A1:AG52"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="30.77734375" customWidth="1" collapsed="1"/>
-    <col min="29" max="29" width="8.77734375" style="3" collapsed="1"/>
+    <col min="2" max="2" customWidth="true" width="30.77734375" collapsed="true"/>
+    <col min="29" max="29" style="3" width="8.77734375" collapsed="true"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:33" ht="28.8" x14ac:dyDescent="0.3">
@@ -18179,11 +19062,11 @@
       </c>
     </row>
     <row r="2" spans="1:33" ht="72" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>63</v>
       </c>
-      <c r="B2" t="s">
-        <v>281</v>
+      <c r="B2" t="s" s="0">
+        <v>672</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>28</v>
@@ -18246,11 +19129,11 @@
       </c>
     </row>
     <row r="3" spans="1:33" ht="72" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
+      <c r="A3" t="s" s="0">
         <v>63</v>
       </c>
-      <c r="B3" t="s">
-        <v>282</v>
+      <c r="B3" t="s" s="0">
+        <v>673</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>28</v>
@@ -18313,11 +19196,11 @@
       </c>
     </row>
     <row r="4" spans="1:33" ht="72" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
+      <c r="A4" t="s" s="0">
         <v>63</v>
       </c>
-      <c r="B4" t="s">
-        <v>283</v>
+      <c r="B4" t="s" s="0">
+        <v>674</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>28</v>
@@ -18380,11 +19263,11 @@
       </c>
     </row>
     <row r="5" spans="1:33" ht="72" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
+      <c r="A5" t="s" s="0">
         <v>63</v>
       </c>
-      <c r="B5" t="s">
-        <v>284</v>
+      <c r="B5" t="s" s="0">
+        <v>675</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>28</v>
@@ -18447,11 +19330,11 @@
       </c>
     </row>
     <row r="6" spans="1:33" ht="72" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
+      <c r="A6" t="s" s="0">
         <v>63</v>
       </c>
-      <c r="B6" t="s">
-        <v>285</v>
+      <c r="B6" t="s" s="0">
+        <v>676</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>28</v>
@@ -18514,11 +19397,11 @@
       </c>
     </row>
     <row r="7" spans="1:33" ht="72" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
-        <v>63</v>
-      </c>
-      <c r="B7" t="s">
-        <v>286</v>
+      <c r="A7" t="s" s="0">
+        <v>177</v>
+      </c>
+      <c r="B7" t="s" s="0">
+        <v>677</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>28</v>
@@ -18581,11 +19464,11 @@
       </c>
     </row>
     <row r="8" spans="1:33" ht="72" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
+      <c r="A8" t="s" s="0">
         <v>63</v>
       </c>
-      <c r="B8" t="s">
-        <v>287</v>
+      <c r="B8" t="s" s="0">
+        <v>678</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>28</v>
@@ -18648,11 +19531,11 @@
       </c>
     </row>
     <row r="9" spans="1:33" ht="72" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
+      <c r="A9" t="s" s="0">
         <v>63</v>
       </c>
-      <c r="B9" t="s">
-        <v>288</v>
+      <c r="B9" t="s" s="0">
+        <v>679</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>28</v>
@@ -18715,11 +19598,11 @@
       </c>
     </row>
     <row r="10" spans="1:33" ht="72" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
+      <c r="A10" t="s" s="0">
         <v>63</v>
       </c>
-      <c r="B10" t="s">
-        <v>289</v>
+      <c r="B10" t="s" s="0">
+        <v>680</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>28</v>
@@ -18782,11 +19665,11 @@
       </c>
     </row>
     <row r="11" spans="1:33" ht="72" x14ac:dyDescent="0.3">
-      <c r="A11" t="s">
+      <c r="A11" t="s" s="0">
         <v>63</v>
       </c>
-      <c r="B11" t="s">
-        <v>290</v>
+      <c r="B11" t="s" s="0">
+        <v>681</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>28</v>
@@ -18849,11 +19732,11 @@
       </c>
     </row>
     <row r="12" spans="1:33" ht="72" x14ac:dyDescent="0.3">
-      <c r="A12" t="s">
+      <c r="A12" t="s" s="0">
         <v>63</v>
       </c>
-      <c r="B12" t="s">
-        <v>291</v>
+      <c r="B12" t="s" s="0">
+        <v>682</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>28</v>
@@ -18916,11 +19799,11 @@
       </c>
     </row>
     <row r="13" spans="1:33" ht="72" x14ac:dyDescent="0.3">
-      <c r="A13" t="s">
+      <c r="A13" t="s" s="0">
         <v>63</v>
       </c>
-      <c r="B13" t="s">
-        <v>292</v>
+      <c r="B13" t="s" s="0">
+        <v>683</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>28</v>
@@ -18983,11 +19866,11 @@
       </c>
     </row>
     <row r="14" spans="1:33" ht="72" x14ac:dyDescent="0.3">
-      <c r="A14" t="s">
+      <c r="A14" t="s" s="0">
         <v>63</v>
       </c>
-      <c r="B14" t="s">
-        <v>293</v>
+      <c r="B14" t="s" s="0">
+        <v>684</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>28</v>
@@ -19050,11 +19933,11 @@
       </c>
     </row>
     <row r="15" spans="1:33" ht="72" x14ac:dyDescent="0.3">
-      <c r="A15" t="s">
+      <c r="A15" t="s" s="0">
         <v>63</v>
       </c>
-      <c r="B15" t="s">
-        <v>294</v>
+      <c r="B15" t="s" s="0">
+        <v>685</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>28</v>
@@ -19117,11 +20000,11 @@
       </c>
     </row>
     <row r="16" spans="1:33" ht="72" x14ac:dyDescent="0.3">
-      <c r="A16" t="s">
+      <c r="A16" t="s" s="0">
         <v>63</v>
       </c>
-      <c r="B16" t="s">
-        <v>295</v>
+      <c r="B16" t="s" s="0">
+        <v>686</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>28</v>
@@ -19184,11 +20067,11 @@
       </c>
     </row>
     <row r="17" spans="1:33" ht="72" x14ac:dyDescent="0.3">
-      <c r="A17" t="s">
+      <c r="A17" t="s" s="0">
         <v>63</v>
       </c>
-      <c r="B17" t="s">
-        <v>296</v>
+      <c r="B17" t="s" s="0">
+        <v>687</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>28</v>
@@ -19251,11 +20134,11 @@
       </c>
     </row>
     <row r="18" spans="1:33" ht="72" x14ac:dyDescent="0.3">
-      <c r="A18" t="s">
+      <c r="A18" t="s" s="0">
         <v>63</v>
       </c>
-      <c r="B18" t="s">
-        <v>297</v>
+      <c r="B18" t="s" s="0">
+        <v>688</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>28</v>
@@ -19318,11 +20201,11 @@
       </c>
     </row>
     <row r="19" spans="1:33" ht="72" x14ac:dyDescent="0.3">
-      <c r="A19" t="s">
+      <c r="A19" t="s" s="0">
         <v>63</v>
       </c>
-      <c r="B19" t="s">
-        <v>298</v>
+      <c r="B19" t="s" s="0">
+        <v>689</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>28</v>
@@ -19385,11 +20268,11 @@
       </c>
     </row>
     <row r="20" spans="1:33" ht="72" x14ac:dyDescent="0.3">
-      <c r="A20" t="s">
+      <c r="A20" t="s" s="0">
         <v>63</v>
       </c>
-      <c r="B20" t="s">
-        <v>299</v>
+      <c r="B20" t="s" s="0">
+        <v>690</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>28</v>
@@ -19452,11 +20335,11 @@
       </c>
     </row>
     <row r="21" spans="1:33" ht="72" x14ac:dyDescent="0.3">
-      <c r="A21" t="s">
+      <c r="A21" t="s" s="0">
         <v>63</v>
       </c>
-      <c r="B21" t="s">
-        <v>300</v>
+      <c r="B21" t="s" s="0">
+        <v>691</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>28</v>
@@ -19519,11 +20402,11 @@
       </c>
     </row>
     <row r="22" spans="1:33" ht="72" x14ac:dyDescent="0.3">
-      <c r="A22" t="s">
+      <c r="A22" t="s" s="0">
         <v>63</v>
       </c>
-      <c r="B22" t="s">
-        <v>301</v>
+      <c r="B22" t="s" s="0">
+        <v>692</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>28</v>
@@ -19586,11 +20469,11 @@
       </c>
     </row>
     <row r="23" spans="1:33" ht="72" x14ac:dyDescent="0.3">
-      <c r="A23" t="s">
+      <c r="A23" t="s" s="0">
         <v>63</v>
       </c>
-      <c r="B23" t="s">
-        <v>302</v>
+      <c r="B23" t="s" s="0">
+        <v>693</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>28</v>
@@ -19653,11 +20536,11 @@
       </c>
     </row>
     <row r="24" spans="1:33" ht="72" x14ac:dyDescent="0.3">
-      <c r="A24" t="s">
+      <c r="A24" t="s" s="0">
         <v>63</v>
       </c>
-      <c r="B24" t="s">
-        <v>303</v>
+      <c r="B24" t="s" s="0">
+        <v>694</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>28</v>
@@ -19720,11 +20603,11 @@
       </c>
     </row>
     <row r="25" spans="1:33" ht="72" x14ac:dyDescent="0.3">
-      <c r="A25" t="s">
-        <v>63</v>
-      </c>
-      <c r="B25" t="s">
-        <v>304</v>
+      <c r="A25" t="s" s="0">
+        <v>177</v>
+      </c>
+      <c r="B25" t="s" s="0">
+        <v>695</v>
       </c>
       <c r="C25" s="1" t="s">
         <v>28</v>
@@ -19787,11 +20670,11 @@
       </c>
     </row>
     <row r="26" spans="1:33" ht="72" x14ac:dyDescent="0.3">
-      <c r="A26" t="s">
+      <c r="A26" t="s" s="0">
         <v>63</v>
       </c>
-      <c r="B26" t="s">
-        <v>305</v>
+      <c r="B26" t="s" s="0">
+        <v>696</v>
       </c>
       <c r="C26" s="1" t="s">
         <v>28</v>
@@ -19854,11 +20737,11 @@
       </c>
     </row>
     <row r="27" spans="1:33" ht="72" x14ac:dyDescent="0.3">
-      <c r="A27" t="s">
+      <c r="A27" t="s" s="0">
         <v>63</v>
       </c>
-      <c r="B27" t="s">
-        <v>306</v>
+      <c r="B27" t="s" s="0">
+        <v>697</v>
       </c>
       <c r="C27" s="1" t="s">
         <v>28</v>
@@ -19921,11 +20804,11 @@
       </c>
     </row>
     <row r="28" spans="1:33" ht="72" x14ac:dyDescent="0.3">
-      <c r="A28" t="s">
+      <c r="A28" t="s" s="0">
         <v>63</v>
       </c>
-      <c r="B28" t="s">
-        <v>307</v>
+      <c r="B28" t="s" s="0">
+        <v>698</v>
       </c>
       <c r="C28" s="1" t="s">
         <v>28</v>
@@ -19988,11 +20871,11 @@
       </c>
     </row>
     <row r="29" spans="1:33" ht="72" x14ac:dyDescent="0.3">
-      <c r="A29" t="s">
+      <c r="A29" t="s" s="0">
         <v>63</v>
       </c>
-      <c r="B29" t="s">
-        <v>308</v>
+      <c r="B29" t="s" s="0">
+        <v>699</v>
       </c>
       <c r="C29" s="1" t="s">
         <v>28</v>
@@ -20055,11 +20938,11 @@
       </c>
     </row>
     <row r="30" spans="1:33" ht="72" x14ac:dyDescent="0.3">
-      <c r="A30" t="s">
+      <c r="A30" t="s" s="0">
         <v>63</v>
       </c>
-      <c r="B30" t="s">
-        <v>309</v>
+      <c r="B30" t="s" s="0">
+        <v>700</v>
       </c>
       <c r="C30" s="1" t="s">
         <v>28</v>
@@ -20122,11 +21005,11 @@
       </c>
     </row>
     <row r="31" spans="1:33" ht="72" x14ac:dyDescent="0.3">
-      <c r="A31" t="s">
+      <c r="A31" t="s" s="0">
         <v>63</v>
       </c>
-      <c r="B31" t="s">
-        <v>310</v>
+      <c r="B31" t="s" s="0">
+        <v>701</v>
       </c>
       <c r="C31" s="1" t="s">
         <v>28</v>
@@ -20189,11 +21072,11 @@
       </c>
     </row>
     <row r="32" spans="1:33" ht="72" x14ac:dyDescent="0.3">
-      <c r="A32" t="s">
+      <c r="A32" t="s" s="0">
         <v>63</v>
       </c>
-      <c r="B32" t="s">
-        <v>311</v>
+      <c r="B32" t="s" s="0">
+        <v>702</v>
       </c>
       <c r="C32" s="1" t="s">
         <v>28</v>
@@ -20256,11 +21139,11 @@
       </c>
     </row>
     <row r="33" spans="1:33" ht="72" x14ac:dyDescent="0.3">
-      <c r="A33" t="s">
+      <c r="A33" t="s" s="0">
         <v>63</v>
       </c>
-      <c r="B33" t="s">
-        <v>312</v>
+      <c r="B33" t="s" s="0">
+        <v>703</v>
       </c>
       <c r="C33" s="1" t="s">
         <v>28</v>
@@ -20323,11 +21206,11 @@
       </c>
     </row>
     <row r="34" spans="1:33" ht="72" x14ac:dyDescent="0.3">
-      <c r="A34" t="s">
-        <v>177</v>
-      </c>
-      <c r="B34" t="s">
-        <v>313</v>
+      <c r="A34" t="s" s="0">
+        <v>63</v>
+      </c>
+      <c r="B34" t="s" s="0">
+        <v>704</v>
       </c>
       <c r="C34" s="1" t="s">
         <v>28</v>
@@ -20390,11 +21273,11 @@
       </c>
     </row>
     <row r="35" spans="1:33" ht="72" x14ac:dyDescent="0.3">
-      <c r="A35" t="s">
-        <v>177</v>
-      </c>
-      <c r="B35" t="s">
-        <v>314</v>
+      <c r="A35" t="s" s="0">
+        <v>63</v>
+      </c>
+      <c r="B35" t="s" s="0">
+        <v>705</v>
       </c>
       <c r="C35" s="1" t="s">
         <v>28</v>
@@ -20457,11 +21340,11 @@
       </c>
     </row>
     <row r="36" spans="1:33" ht="72" x14ac:dyDescent="0.3">
-      <c r="A36" t="s">
-        <v>177</v>
-      </c>
-      <c r="B36" t="s">
-        <v>315</v>
+      <c r="A36" t="s" s="0">
+        <v>63</v>
+      </c>
+      <c r="B36" t="s" s="0">
+        <v>706</v>
       </c>
       <c r="C36" s="1" t="s">
         <v>28</v>
@@ -20524,11 +21407,11 @@
       </c>
     </row>
     <row r="37" spans="1:33" ht="72" x14ac:dyDescent="0.3">
-      <c r="A37" t="s">
-        <v>177</v>
-      </c>
-      <c r="B37" t="s">
-        <v>316</v>
+      <c r="A37" t="s" s="0">
+        <v>63</v>
+      </c>
+      <c r="B37" t="s" s="0">
+        <v>707</v>
       </c>
       <c r="C37" s="1" t="s">
         <v>28</v>
@@ -20591,11 +21474,11 @@
       </c>
     </row>
     <row r="38" spans="1:33" ht="72" x14ac:dyDescent="0.3">
-      <c r="A38" t="s">
-        <v>177</v>
-      </c>
-      <c r="B38" t="s">
-        <v>317</v>
+      <c r="A38" t="s" s="0">
+        <v>63</v>
+      </c>
+      <c r="B38" t="s" s="0">
+        <v>708</v>
       </c>
       <c r="C38" s="1" t="s">
         <v>28</v>
@@ -20658,11 +21541,11 @@
       </c>
     </row>
     <row r="39" spans="1:33" ht="72" x14ac:dyDescent="0.3">
-      <c r="A39" t="s">
-        <v>177</v>
-      </c>
-      <c r="B39" t="s">
-        <v>318</v>
+      <c r="A39" t="s" s="0">
+        <v>63</v>
+      </c>
+      <c r="B39" t="s" s="0">
+        <v>709</v>
       </c>
       <c r="C39" s="1" t="s">
         <v>28</v>
@@ -20725,11 +21608,11 @@
       </c>
     </row>
     <row r="40" spans="1:33" ht="72" x14ac:dyDescent="0.3">
-      <c r="A40" t="s">
-        <v>177</v>
-      </c>
-      <c r="B40" t="s">
-        <v>319</v>
+      <c r="A40" t="s" s="0">
+        <v>63</v>
+      </c>
+      <c r="B40" t="s" s="0">
+        <v>710</v>
       </c>
       <c r="C40" s="1" t="s">
         <v>28</v>
@@ -20792,11 +21675,11 @@
       </c>
     </row>
     <row r="41" spans="1:33" ht="72" x14ac:dyDescent="0.3">
-      <c r="A41" t="s">
-        <v>177</v>
-      </c>
-      <c r="B41" t="s">
-        <v>320</v>
+      <c r="A41" t="s" s="0">
+        <v>63</v>
+      </c>
+      <c r="B41" t="s" s="0">
+        <v>711</v>
       </c>
       <c r="C41" s="1" t="s">
         <v>28</v>
@@ -20859,11 +21742,11 @@
       </c>
     </row>
     <row r="42" spans="1:33" ht="72" x14ac:dyDescent="0.3">
-      <c r="A42" t="s">
+      <c r="A42" t="s" s="0">
         <v>63</v>
       </c>
-      <c r="B42" t="s">
-        <v>321</v>
+      <c r="B42" t="s" s="0">
+        <v>712</v>
       </c>
       <c r="C42" s="1" t="s">
         <v>28</v>
@@ -20926,11 +21809,11 @@
       </c>
     </row>
     <row r="43" spans="1:33" ht="72" x14ac:dyDescent="0.3">
-      <c r="A43" t="s">
+      <c r="A43" t="s" s="0">
         <v>63</v>
       </c>
-      <c r="B43" t="s">
-        <v>322</v>
+      <c r="B43" t="s" s="0">
+        <v>713</v>
       </c>
       <c r="C43" s="1" t="s">
         <v>28</v>
@@ -20993,11 +21876,11 @@
       </c>
     </row>
     <row r="44" spans="1:33" ht="72" x14ac:dyDescent="0.3">
-      <c r="A44" t="s">
+      <c r="A44" t="s" s="0">
         <v>63</v>
       </c>
-      <c r="B44" t="s">
-        <v>323</v>
+      <c r="B44" t="s" s="0">
+        <v>714</v>
       </c>
       <c r="C44" s="1" t="s">
         <v>28</v>
@@ -21060,11 +21943,11 @@
       </c>
     </row>
     <row r="45" spans="1:33" ht="72" x14ac:dyDescent="0.3">
-      <c r="A45" t="s">
+      <c r="A45" t="s" s="0">
         <v>63</v>
       </c>
-      <c r="B45" t="s">
-        <v>324</v>
+      <c r="B45" t="s" s="0">
+        <v>715</v>
       </c>
       <c r="C45" s="1" t="s">
         <v>28</v>
@@ -21127,11 +22010,11 @@
       </c>
     </row>
     <row r="46" spans="1:33" ht="72" x14ac:dyDescent="0.3">
-      <c r="A46" t="s">
+      <c r="A46" t="s" s="0">
         <v>63</v>
       </c>
-      <c r="B46" t="s">
-        <v>325</v>
+      <c r="B46" t="s" s="0">
+        <v>716</v>
       </c>
       <c r="C46" s="1" t="s">
         <v>28</v>
@@ -21194,11 +22077,11 @@
       </c>
     </row>
     <row r="47" spans="1:33" ht="72" x14ac:dyDescent="0.3">
-      <c r="A47" t="s">
+      <c r="A47" t="s" s="0">
         <v>63</v>
       </c>
-      <c r="B47" t="s">
-        <v>326</v>
+      <c r="B47" t="s" s="0">
+        <v>717</v>
       </c>
       <c r="C47" s="1" t="s">
         <v>28</v>
@@ -21261,11 +22144,11 @@
       </c>
     </row>
     <row r="48" spans="1:33" ht="72" x14ac:dyDescent="0.3">
-      <c r="A48" t="s">
+      <c r="A48" t="s" s="0">
         <v>63</v>
       </c>
-      <c r="B48" t="s">
-        <v>327</v>
+      <c r="B48" t="s" s="0">
+        <v>718</v>
       </c>
       <c r="C48" s="1" t="s">
         <v>28</v>
@@ -21328,11 +22211,11 @@
       </c>
     </row>
     <row r="49" spans="1:33" ht="72" x14ac:dyDescent="0.3">
-      <c r="A49" t="s">
+      <c r="A49" t="s" s="0">
         <v>63</v>
       </c>
-      <c r="B49" t="s">
-        <v>328</v>
+      <c r="B49" t="s" s="0">
+        <v>719</v>
       </c>
       <c r="C49" s="1" t="s">
         <v>28</v>
@@ -21395,11 +22278,11 @@
       </c>
     </row>
     <row r="50" spans="1:33" ht="72" x14ac:dyDescent="0.3">
-      <c r="A50" t="s">
+      <c r="A50" t="s" s="0">
         <v>63</v>
       </c>
-      <c r="B50" t="s">
-        <v>329</v>
+      <c r="B50" t="s" s="0">
+        <v>720</v>
       </c>
       <c r="C50" s="1" t="s">
         <v>28</v>
@@ -21478,12 +22361,12 @@
   <dimension ref="A1:AG10"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="25.44140625" customWidth="1" collapsed="1"/>
-    <col min="20" max="20" width="10" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="21" max="22" width="9" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="23" max="23" width="10" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="29" max="29" width="8.77734375" style="3" collapsed="1"/>
-    <col min="31" max="32" width="9" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="2" max="2" customWidth="true" width="25.44140625" collapsed="true"/>
+    <col min="20" max="20" bestFit="true" customWidth="true" width="10.0" collapsed="true"/>
+    <col min="21" max="22" bestFit="true" customWidth="true" width="9.0" collapsed="true"/>
+    <col min="23" max="23" bestFit="true" customWidth="true" width="10.0" collapsed="true"/>
+    <col min="29" max="29" style="3" width="8.77734375" collapsed="true"/>
+    <col min="31" max="32" bestFit="true" customWidth="true" width="9.0" collapsed="true"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:33" ht="28.8" x14ac:dyDescent="0.3">
@@ -21588,11 +22471,11 @@
       </c>
     </row>
     <row r="2" spans="1:33" ht="72" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>63</v>
       </c>
-      <c r="B2" t="s">
-        <v>330</v>
+      <c r="B2" t="s" s="0">
+        <v>575</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>47</v>
@@ -21655,11 +22538,11 @@
       </c>
     </row>
     <row r="3" spans="1:33" ht="72" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
+      <c r="A3" t="s" s="0">
         <v>63</v>
       </c>
-      <c r="B3" t="s">
-        <v>331</v>
+      <c r="B3" t="s" s="0">
+        <v>576</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>47</v>
@@ -21722,11 +22605,11 @@
       </c>
     </row>
     <row r="4" spans="1:33" ht="72" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
+      <c r="A4" t="s" s="0">
         <v>63</v>
       </c>
-      <c r="B4" t="s">
-        <v>332</v>
+      <c r="B4" t="s" s="0">
+        <v>577</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>47</v>
@@ -21789,11 +22672,11 @@
       </c>
     </row>
     <row r="5" spans="1:33" ht="72" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
+      <c r="A5" t="s" s="0">
         <v>63</v>
       </c>
-      <c r="B5" t="s">
-        <v>333</v>
+      <c r="B5" t="s" s="0">
+        <v>578</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>47</v>
@@ -21856,11 +22739,11 @@
       </c>
     </row>
     <row r="6" spans="1:33" ht="72" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
+      <c r="A6" t="s" s="0">
         <v>63</v>
       </c>
-      <c r="B6" t="s">
-        <v>334</v>
+      <c r="B6" t="s" s="0">
+        <v>579</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>47</v>
@@ -21923,11 +22806,11 @@
       </c>
     </row>
     <row r="7" spans="1:33" ht="72" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
+      <c r="A7" t="s" s="0">
         <v>63</v>
       </c>
-      <c r="B7" t="s">
-        <v>335</v>
+      <c r="B7" t="s" s="0">
+        <v>580</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>47</v>
@@ -21990,11 +22873,11 @@
       </c>
     </row>
     <row r="8" spans="1:33" ht="72" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
+      <c r="A8" t="s" s="0">
         <v>63</v>
       </c>
-      <c r="B8" t="s">
-        <v>336</v>
+      <c r="B8" t="s" s="0">
+        <v>581</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>47</v>
@@ -22057,11 +22940,11 @@
       </c>
     </row>
     <row r="9" spans="1:33" ht="72" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
+      <c r="A9" t="s" s="0">
         <v>63</v>
       </c>
-      <c r="B9" t="s">
-        <v>337</v>
+      <c r="B9" t="s" s="0">
+        <v>582</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>47</v>
@@ -22124,11 +23007,11 @@
       </c>
     </row>
     <row r="10" spans="1:33" ht="72" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
+      <c r="A10" t="s" s="0">
         <v>63</v>
       </c>
-      <c r="B10" t="s">
-        <v>338</v>
+      <c r="B10" t="s" s="0">
+        <v>583</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>47</v>
@@ -22201,11 +23084,11 @@
   <dimension ref="A1:AG52"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="20" max="20" width="10" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="21" max="22" width="9" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="23" max="23" width="10" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="29" max="29" width="8.77734375" style="3" collapsed="1"/>
-    <col min="31" max="32" width="9" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="20" max="20" bestFit="true" customWidth="true" width="10.0" collapsed="true"/>
+    <col min="21" max="22" bestFit="true" customWidth="true" width="9.0" collapsed="true"/>
+    <col min="23" max="23" bestFit="true" customWidth="true" width="10.0" collapsed="true"/>
+    <col min="29" max="29" style="3" width="8.77734375" collapsed="true"/>
+    <col min="31" max="32" bestFit="true" customWidth="true" width="9.0" collapsed="true"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:33" ht="28.8" x14ac:dyDescent="0.3">
@@ -22310,11 +23193,11 @@
       </c>
     </row>
     <row r="2" spans="1:33" ht="72" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>63</v>
       </c>
-      <c r="B2" t="s">
-        <v>339</v>
+      <c r="B2" t="s" s="0">
+        <v>584</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>47</v>
@@ -22377,11 +23260,11 @@
       </c>
     </row>
     <row r="3" spans="1:33" ht="72" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
+      <c r="A3" t="s" s="0">
         <v>63</v>
       </c>
-      <c r="B3" t="s">
-        <v>340</v>
+      <c r="B3" t="s" s="0">
+        <v>585</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>47</v>
@@ -22444,11 +23327,11 @@
       </c>
     </row>
     <row r="4" spans="1:33" ht="72" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
+      <c r="A4" t="s" s="0">
         <v>63</v>
       </c>
-      <c r="B4" t="s">
-        <v>341</v>
+      <c r="B4" t="s" s="0">
+        <v>586</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>47</v>
@@ -22511,11 +23394,11 @@
       </c>
     </row>
     <row r="5" spans="1:33" ht="72" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
+      <c r="A5" t="s" s="0">
         <v>63</v>
       </c>
-      <c r="B5" t="s">
-        <v>342</v>
+      <c r="B5" t="s" s="0">
+        <v>587</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>47</v>
@@ -22578,11 +23461,11 @@
       </c>
     </row>
     <row r="6" spans="1:33" ht="72" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
+      <c r="A6" t="s" s="0">
         <v>63</v>
       </c>
-      <c r="B6" t="s">
-        <v>343</v>
+      <c r="B6" t="s" s="0">
+        <v>588</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>47</v>
@@ -22645,11 +23528,11 @@
       </c>
     </row>
     <row r="7" spans="1:33" ht="72" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
+      <c r="A7" t="s" s="0">
         <v>63</v>
       </c>
-      <c r="B7" t="s">
-        <v>344</v>
+      <c r="B7" t="s" s="0">
+        <v>589</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>47</v>
@@ -22712,11 +23595,11 @@
       </c>
     </row>
     <row r="8" spans="1:33" ht="72" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
+      <c r="A8" t="s" s="0">
         <v>63</v>
       </c>
-      <c r="B8" t="s">
-        <v>345</v>
+      <c r="B8" t="s" s="0">
+        <v>590</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>47</v>
@@ -22779,11 +23662,11 @@
       </c>
     </row>
     <row r="9" spans="1:33" ht="72" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
+      <c r="A9" t="s" s="0">
         <v>63</v>
       </c>
-      <c r="B9" t="s">
-        <v>346</v>
+      <c r="B9" t="s" s="0">
+        <v>591</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>47</v>
@@ -22846,11 +23729,11 @@
       </c>
     </row>
     <row r="10" spans="1:33" ht="72" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
+      <c r="A10" t="s" s="0">
         <v>63</v>
       </c>
-      <c r="B10" t="s">
-        <v>347</v>
+      <c r="B10" t="s" s="0">
+        <v>592</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>47</v>
@@ -23049,12 +23932,12 @@
   <dimension ref="A1:AG52"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="37.44140625" customWidth="1" collapsed="1"/>
-    <col min="20" max="20" width="10" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="21" max="22" width="9" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="23" max="23" width="10" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="29" max="29" width="8.77734375" style="3" collapsed="1"/>
-    <col min="31" max="32" width="9" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="2" max="2" customWidth="true" width="37.44140625" collapsed="true"/>
+    <col min="20" max="20" bestFit="true" customWidth="true" width="10.0" collapsed="true"/>
+    <col min="21" max="22" bestFit="true" customWidth="true" width="9.0" collapsed="true"/>
+    <col min="23" max="23" bestFit="true" customWidth="true" width="10.0" collapsed="true"/>
+    <col min="29" max="29" style="3" width="8.77734375" collapsed="true"/>
+    <col min="31" max="32" bestFit="true" customWidth="true" width="9.0" collapsed="true"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:33" ht="28.8" x14ac:dyDescent="0.3">
@@ -23159,11 +24042,11 @@
       </c>
     </row>
     <row r="2" spans="1:33" ht="72" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>63</v>
       </c>
-      <c r="B2" t="s">
-        <v>348</v>
+      <c r="B2" t="s" s="0">
+        <v>593</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>47</v>
@@ -23226,10 +24109,10 @@
       </c>
     </row>
     <row r="3" spans="1:33" ht="72" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
+      <c r="A3" t="s" s="0">
         <v>177</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" t="s" s="0">
         <v>180</v>
       </c>
       <c r="C3" s="1" t="s">
@@ -23293,10 +24176,10 @@
       </c>
     </row>
     <row r="4" spans="1:33" ht="72" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
+      <c r="A4" t="s" s="0">
         <v>63</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" t="s" s="0">
         <v>174</v>
       </c>
       <c r="C4" s="1" t="s">
@@ -23360,10 +24243,10 @@
       </c>
     </row>
     <row r="5" spans="1:33" ht="72" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
+      <c r="A5" t="s" s="0">
         <v>63</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" t="s" s="0">
         <v>120</v>
       </c>
       <c r="C5" s="1" t="s">
@@ -23427,10 +24310,10 @@
       </c>
     </row>
     <row r="6" spans="1:33" ht="72" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
+      <c r="A6" t="s" s="0">
         <v>63</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B6" t="s" s="0">
         <v>175</v>
       </c>
       <c r="C6" s="1" t="s">
@@ -23494,10 +24377,10 @@
       </c>
     </row>
     <row r="7" spans="1:33" ht="72" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
+      <c r="A7" t="s" s="0">
         <v>63</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" t="s" s="0">
         <v>121</v>
       </c>
       <c r="C7" s="1" t="s">
@@ -23561,10 +24444,10 @@
       </c>
     </row>
     <row r="8" spans="1:33" ht="72" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
+      <c r="A8" t="s" s="0">
         <v>63</v>
       </c>
-      <c r="B8" t="s">
+      <c r="B8" t="s" s="0">
         <v>122</v>
       </c>
       <c r="C8" s="1" t="s">
@@ -23628,10 +24511,10 @@
       </c>
     </row>
     <row r="9" spans="1:33" ht="72" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
+      <c r="A9" t="s" s="0">
         <v>63</v>
       </c>
-      <c r="B9" t="s">
+      <c r="B9" t="s" s="0">
         <v>176</v>
       </c>
       <c r="C9" s="1" t="s">
@@ -23695,10 +24578,10 @@
       </c>
     </row>
     <row r="10" spans="1:33" ht="72" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
+      <c r="A10" t="s" s="0">
         <v>63</v>
       </c>
-      <c r="B10" t="s">
+      <c r="B10" t="s" s="0">
         <v>123</v>
       </c>
       <c r="C10" s="1" t="s">
@@ -23898,12 +24781,12 @@
   <dimension ref="A1:AG52"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="22.77734375" customWidth="1" collapsed="1"/>
-    <col min="20" max="20" width="10" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="21" max="22" width="9" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="23" max="23" width="10" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="29" max="29" width="8.77734375" style="3" collapsed="1"/>
-    <col min="31" max="32" width="9" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="2" max="2" customWidth="true" width="22.77734375" collapsed="true"/>
+    <col min="20" max="20" bestFit="true" customWidth="true" width="10.0" collapsed="true"/>
+    <col min="21" max="22" bestFit="true" customWidth="true" width="9.0" collapsed="true"/>
+    <col min="23" max="23" bestFit="true" customWidth="true" width="10.0" collapsed="true"/>
+    <col min="29" max="29" style="3" width="8.77734375" collapsed="true"/>
+    <col min="31" max="32" bestFit="true" customWidth="true" width="9.0" collapsed="true"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:33" ht="28.8" x14ac:dyDescent="0.3">
@@ -24008,11 +24891,11 @@
       </c>
     </row>
     <row r="2" spans="1:33" ht="72" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>63</v>
       </c>
-      <c r="B2" t="s">
-        <v>349</v>
+      <c r="B2" t="s" s="0">
+        <v>594</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>47</v>
@@ -24075,11 +24958,11 @@
       </c>
     </row>
     <row r="3" spans="1:33" ht="72" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
+      <c r="A3" t="s" s="0">
         <v>63</v>
       </c>
-      <c r="B3" t="s">
-        <v>350</v>
+      <c r="B3" t="s" s="0">
+        <v>595</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>47</v>
@@ -24142,11 +25025,11 @@
       </c>
     </row>
     <row r="4" spans="1:33" ht="72" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
+      <c r="A4" t="s" s="0">
         <v>63</v>
       </c>
-      <c r="B4" t="s">
-        <v>351</v>
+      <c r="B4" t="s" s="0">
+        <v>596</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>47</v>
@@ -24209,11 +25092,11 @@
       </c>
     </row>
     <row r="5" spans="1:33" ht="72" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
+      <c r="A5" t="s" s="0">
         <v>63</v>
       </c>
-      <c r="B5" t="s">
-        <v>352</v>
+      <c r="B5" t="s" s="0">
+        <v>597</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>47</v>
@@ -24276,11 +25159,11 @@
       </c>
     </row>
     <row r="6" spans="1:33" ht="72" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
+      <c r="A6" t="s" s="0">
         <v>63</v>
       </c>
-      <c r="B6" t="s">
-        <v>353</v>
+      <c r="B6" t="s" s="0">
+        <v>598</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>47</v>
@@ -24343,11 +25226,11 @@
       </c>
     </row>
     <row r="7" spans="1:33" ht="72" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
+      <c r="A7" t="s" s="0">
         <v>63</v>
       </c>
-      <c r="B7" t="s">
-        <v>354</v>
+      <c r="B7" t="s" s="0">
+        <v>599</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>47</v>
@@ -24410,11 +25293,11 @@
       </c>
     </row>
     <row r="8" spans="1:33" ht="72" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
+      <c r="A8" t="s" s="0">
         <v>63</v>
       </c>
-      <c r="B8" t="s">
-        <v>355</v>
+      <c r="B8" t="s" s="0">
+        <v>600</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>47</v>
@@ -24477,11 +25360,11 @@
       </c>
     </row>
     <row r="9" spans="1:33" ht="72" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
+      <c r="A9" t="s" s="0">
         <v>63</v>
       </c>
-      <c r="B9" t="s">
-        <v>356</v>
+      <c r="B9" t="s" s="0">
+        <v>601</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>47</v>
@@ -24544,11 +25427,11 @@
       </c>
     </row>
     <row r="10" spans="1:33" ht="72" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
+      <c r="A10" t="s" s="0">
         <v>63</v>
       </c>
-      <c r="B10" t="s">
-        <v>357</v>
+      <c r="B10" t="s" s="0">
+        <v>602</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>47</v>
@@ -24747,10 +25630,10 @@
   <dimension ref="A1:AH52"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="18" customWidth="1" collapsed="1"/>
-    <col min="21" max="21" width="10" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="30" max="30" width="8.77734375" style="3" collapsed="1"/>
-    <col min="32" max="33" width="9" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="2" max="2" customWidth="true" width="18.0" collapsed="true"/>
+    <col min="21" max="21" bestFit="true" customWidth="true" width="10.0" collapsed="true"/>
+    <col min="30" max="30" style="3" width="8.77734375" collapsed="true"/>
+    <col min="32" max="33" bestFit="true" customWidth="true" width="9.0" collapsed="true"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:34" ht="28.8" x14ac:dyDescent="0.3">
@@ -24858,11 +25741,11 @@
       </c>
     </row>
     <row r="2" spans="1:34" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>63</v>
-      </c>
-      <c r="B2" t="s">
-        <v>358</v>
+      <c r="A2" t="s" s="0">
+        <v>177</v>
+      </c>
+      <c r="B2" t="s" s="0">
+        <v>603</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>42</v>
@@ -24926,11 +25809,11 @@
       </c>
     </row>
     <row r="3" spans="1:34" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>63</v>
-      </c>
-      <c r="B3" t="s">
-        <v>359</v>
+      <c r="A3" t="s" s="0">
+        <v>177</v>
+      </c>
+      <c r="B3" t="s" s="0">
+        <v>604</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>42</v>
@@ -24994,11 +25877,11 @@
       </c>
     </row>
     <row r="4" spans="1:34" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>63</v>
-      </c>
-      <c r="B4" t="s">
-        <v>360</v>
+      <c r="A4" t="s" s="0">
+        <v>177</v>
+      </c>
+      <c r="B4" t="s" s="0">
+        <v>605</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>42</v>
@@ -25062,11 +25945,11 @@
       </c>
     </row>
     <row r="5" spans="1:34" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>63</v>
-      </c>
-      <c r="B5" t="s">
-        <v>361</v>
+      <c r="A5" t="s" s="0">
+        <v>177</v>
+      </c>
+      <c r="B5" t="s" s="0">
+        <v>606</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>42</v>
@@ -25130,11 +26013,11 @@
       </c>
     </row>
     <row r="6" spans="1:34" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
-        <v>63</v>
-      </c>
-      <c r="B6" t="s">
-        <v>362</v>
+      <c r="A6" t="s" s="0">
+        <v>177</v>
+      </c>
+      <c r="B6" t="s" s="0">
+        <v>607</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>42</v>
@@ -25198,11 +26081,11 @@
       </c>
     </row>
     <row r="7" spans="1:34" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
-        <v>63</v>
-      </c>
-      <c r="B7" t="s">
-        <v>363</v>
+      <c r="A7" t="s" s="0">
+        <v>177</v>
+      </c>
+      <c r="B7" t="s" s="0">
+        <v>608</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>42</v>
@@ -25266,11 +26149,11 @@
       </c>
     </row>
     <row r="8" spans="1:34" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
-        <v>63</v>
-      </c>
-      <c r="B8" t="s">
-        <v>364</v>
+      <c r="A8" t="s" s="0">
+        <v>177</v>
+      </c>
+      <c r="B8" t="s" s="0">
+        <v>609</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>42</v>
@@ -25334,11 +26217,11 @@
       </c>
     </row>
     <row r="9" spans="1:34" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
-        <v>63</v>
-      </c>
-      <c r="B9" t="s">
-        <v>365</v>
+      <c r="A9" t="s" s="0">
+        <v>177</v>
+      </c>
+      <c r="B9" t="s" s="0">
+        <v>610</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>42</v>
@@ -25402,11 +26285,11 @@
       </c>
     </row>
     <row r="10" spans="1:34" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
-        <v>63</v>
-      </c>
-      <c r="B10" t="s">
-        <v>366</v>
+      <c r="A10" t="s" s="0">
+        <v>177</v>
+      </c>
+      <c r="B10" t="s" s="0">
+        <v>611</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>42</v>
